--- a/data/resources/source/PAP_Bibliotheque_Ressources_Tableur_Maitre_v1.xlsx
+++ b/data/resources/source/PAP_Bibliotheque_Ressources_Tableur_Maitre_v1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3002577\Desktop\APPLICATION PM AP in progress\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3002577\Documents\DEV\PAP\PAP-Plateforme-dev\data\resources\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE93F745-D678-49D9-9D8C-44B8F5E48614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B58AA80-1485-4844-AB47-1FC13109FA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="105" yWindow="7155" windowWidth="24870" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="105" yWindow="7005" windowWidth="24870" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -868,18 +868,9 @@
     <t>https://www.has-sante.fr/upload/docs/application/pdf/2023-11/has-110_doc_usager_activite_physique_fiche_arthrose.pdf</t>
   </si>
   <si>
-    <t>Cette fiche de la Haute Autorité de santé vous apporte des repères sur les bénéfices de l’activité physique, les activités possibles et les précautions à respecter en cas d'arthrose des membres.</t>
-  </si>
-  <si>
-    <t>Fiche patient HAS sur l’activité physique en cas d'arthrose des membres, utilisable comme support d’information et de discussion.</t>
-  </si>
-  <si>
     <t>Fiche HAS remise : « Arthrose des membres – L’activité physique pour votre santé »</t>
   </si>
   <si>
-    <t>Exemple de fiche institutionnelle destinée au patient, utilisable dans une formation sur la prescription d’activité physique en cas d'arthrose des membres.</t>
-  </si>
-  <si>
     <t>has-arthrose-information-001</t>
   </si>
   <si>
@@ -896,6 +887,15 @@
   </si>
   <si>
     <t>Fiche patient de la Haute Autorité de santé présentant les bénéfices, les conditions de pratique et les précautions liées à l’activité physique en cas d’arthrose des membres.</t>
+  </si>
+  <si>
+    <t>Cette fiche de la Haute Autorité de santé vous apporte des repères sur les bénéfices de l’activité physique, les activités possibles et les précautions à respecter en cas d’arthrose des membres.</t>
+  </si>
+  <si>
+    <t>Fiche patient HAS sur l’activité physique en cas d’arthrose des membres, utilisable comme support d’information et de discussion.</t>
+  </si>
+  <si>
+    <t>Exemple de fiche institutionnelle destinée au patient, utilisable dans une formation sur la prescription d’activité physique en cas d’arthrose des membres.</t>
   </si>
 </sst>
 </file>
@@ -1030,18 +1030,6 @@
         </x:ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1075,12 +1063,27 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1165,9 +1168,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1228,7 +1228,7 @@
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="qr_target"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="requires_internet"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="offline_content"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="source_version" dataDxfId="8"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="source_version" dataDxfId="0"/>
     <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="publication_date"/>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="verified_at"/>
     <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="verified_by"/>
@@ -1441,60 +1441,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="15">
-      <c r="A3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
+      <c r="A3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
     </row>
     <row r="8" spans="1:6" ht="15">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:6" ht="28.5">
       <c r="A9" s="3" t="s">
@@ -1545,14 +1545,14 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6" ht="30">
       <c r="A17" s="4" t="s">
@@ -1575,14 +1575,14 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
     </row>
     <row r="20" spans="1:6" ht="30">
       <c r="A20" s="5" t="s">
@@ -1640,30 +1640,30 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1703,7 +1703,7 @@
     <col min="24" max="24" width="12" customWidth="1"/>
     <col min="25" max="25" width="18" customWidth="1"/>
     <col min="26" max="27" width="16" customWidth="1"/>
-    <col min="28" max="28" width="18" style="17" customWidth="1"/>
+    <col min="28" max="28" width="18" style="13" customWidth="1"/>
     <col min="29" max="30" width="16" customWidth="1"/>
     <col min="31" max="32" width="18" customWidth="1"/>
     <col min="33" max="33" width="14" customWidth="1"/>
@@ -1805,7 +1805,7 @@
       <c r="AA1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AB1" s="15" t="s">
+      <c r="AB1" s="11" t="s">
         <v>66</v>
       </c>
       <c r="AC1" s="6" t="s">
@@ -1920,7 +1920,7 @@
       <c r="P2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="8" t="s">
         <v>248</v>
       </c>
       <c r="R2" s="1"/>
@@ -1949,19 +1949,19 @@
       <c r="AA2" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="AB2" s="16" t="s">
+      <c r="AB2" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="AC2" s="13">
+      <c r="AC2" s="9">
         <v>44896</v>
       </c>
-      <c r="AD2" s="14">
+      <c r="AD2" s="10">
         <v>46198</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="AF2" s="14">
+      <c r="AF2" s="10">
         <v>46563</v>
       </c>
       <c r="AG2" s="1" t="s">
@@ -2050,7 +2050,7 @@
       <c r="P3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="8" t="s">
         <v>267</v>
       </c>
       <c r="R3" s="1"/>
@@ -2079,19 +2079,19 @@
       <c r="AA3" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="AB3" s="16" t="s">
+      <c r="AB3" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="AC3" s="13">
+      <c r="AC3" s="9">
         <v>44896</v>
       </c>
-      <c r="AD3" s="14">
+      <c r="AD3" s="10">
         <v>46198</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="AF3" s="14">
+      <c r="AF3" s="10">
         <v>46563</v>
       </c>
       <c r="AG3" s="1" t="s">
@@ -2137,7 +2137,7 @@
     </row>
     <row r="4" spans="1:50" ht="85.5">
       <c r="A4" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>21</v>
@@ -2146,10 +2146,10 @@
         <v>276</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>90</v>
@@ -2180,48 +2180,48 @@
       <c r="P4" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="Q4" s="12" t="s">
+      <c r="Q4" s="8" t="s">
         <v>278</v>
       </c>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="V4" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="U4" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="W4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="X4" s="18" t="b">
+        <v>288</v>
+      </c>
+      <c r="X4" s="14" t="b">
         <v>1</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Z4" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="18" t="b">
+      <c r="Z4" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="AB4" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="AC4" s="20">
+      <c r="AB4" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="AC4" s="16">
         <v>45231</v>
       </c>
-      <c r="AD4" s="21">
+      <c r="AD4" s="17">
         <v>46198</v>
       </c>
       <c r="AE4" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="AF4" s="21">
+      <c r="AF4" s="17">
         <v>46563</v>
       </c>
       <c r="AG4" s="2" t="s">
@@ -2236,9 +2236,9 @@
       </c>
       <c r="AK4" s="2"/>
       <c r="AL4" t="s">
-        <v>286</v>
-      </c>
-      <c r="AM4" s="18" t="b">
+        <v>283</v>
+      </c>
+      <c r="AM4" s="14" t="b">
         <v>1</v>
       </c>
       <c r="AN4" s="2" t="s">
@@ -2259,7 +2259,7 @@
         <v>30</v>
       </c>
       <c r="AW4" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AX4" s="2" t="s">
         <v>257</v>
@@ -2333,7 +2333,7 @@
       <c r="AA5" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="AB5" s="16"/>
+      <c r="AB5" s="12"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
@@ -2451,7 +2451,7 @@
       <c r="AA6" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="AB6" s="16"/>
+      <c r="AB6" s="12"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
@@ -2503,34 +2503,34 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2 B5:B502">
-    <cfRule type="expression" dxfId="7" priority="9">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>B2="active"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="10">
+    <cfRule type="expression" dxfId="7" priority="10">
       <formula>B2="draft"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="11">
+    <cfRule type="expression" dxfId="6" priority="11">
       <formula>OR(B2="inactive",B2="obsolete",B2="archived")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2 AG5:AG502">
-    <cfRule type="expression" dxfId="4" priority="12">
+    <cfRule type="expression" dxfId="5" priority="12">
       <formula>AG2="broken"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B4">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>B3="active"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>B3="draft"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>OR(B3="inactive",B3="obsolete",B3="archived")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG3:AG4">
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>AG3="broken"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3038,16 +3038,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="4" t="s">

--- a/data/resources/source/PAP_Bibliotheque_Ressources_Tableur_Maitre_v1.xlsx
+++ b/data/resources/source/PAP_Bibliotheque_Ressources_Tableur_Maitre_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3002577\Desktop\APPLICATION PM AP in progress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD0DD83B-2511-4E40-BE17-03BE885269EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8749042-9201-4684-A288-970F535C66D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="330" yWindow="780" windowWidth="24870" windowHeight="8025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2794" uniqueCount="1033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="1072">
   <si>
     <t>Bibliothèque de ressources PAP — Tableur maître</t>
   </si>
@@ -2194,6 +2194,537 @@
     <t>handicap-intellectuel|synthese|has|prescription_activite_physique|apa|professionnel</t>
   </si>
   <si>
+    <t>move50plus-site-principal-001</t>
+  </si>
+  <si>
+    <t>Move50+ - site principal</t>
+  </si>
+  <si>
+    <t>Site Move50+ proposant des programmes d’exercices, un outil d’orientation et des ressources pour rester actif après 50 ans.</t>
+  </si>
+  <si>
+    <t>Move50+ / Sercovie</t>
+  </si>
+  <si>
+    <t>practical_guide</t>
+  </si>
+  <si>
+    <t>patient|clinician|learner|apa_professional</t>
+  </si>
+  <si>
+    <t>consultation_context|patient_library|clinician_library|training_interface|reference_use</t>
+  </si>
+  <si>
+    <t>endurance|renforcement|souplesse|equilibre|motivation|securite|progressivite</t>
+  </si>
+  <si>
+    <t>geriatrie|medecine_generale|medecine_sport|apa</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/</t>
+  </si>
+  <si>
+    <t>Move50+ propose des programmes d’exercices et des ressources pratiques pour bouger plus, notamment après 50 ans.</t>
+  </si>
+  <si>
+    <t>Site ressource Move50+ utilisable comme bibliothèque de programmes et supports patients.</t>
+  </si>
+  <si>
+    <t>Exemple de plateforme externe de programmes d’activité physique pour patients de plus de 50 ans.</t>
+  </si>
+  <si>
+    <t>Site consulté en juin 2026</t>
+  </si>
+  <si>
+    <t>personne_agee|motivation|reference</t>
+  </si>
+  <si>
+    <t>patient_material_example|reference|additional_reading</t>
+  </si>
+  <si>
+    <t>move50plus|seniors|personne_agee|programme|activite_physique|exercise</t>
+  </si>
+  <si>
+    <t>Ressource externe Move50+ identifiée depuis la fiche patient PAP et les pages Move50+ le 29/06/2026. Ressource non hébergée dans le dépôt PAP.</t>
+  </si>
+  <si>
+    <t>move50plus-questionnaire-orientation-001</t>
+  </si>
+  <si>
+    <t>Move50+ - questionnaire d’orientation vers un programme</t>
+  </si>
+  <si>
+    <t>Move50+ - questionnaire</t>
+  </si>
+  <si>
+    <t>Questionnaire Move50+ guidant le choix d’un programme d’exercices selon la condition physique.</t>
+  </si>
+  <si>
+    <t>self_assessment</t>
+  </si>
+  <si>
+    <t>motivation|securite|progressivite</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/questionnaire/</t>
+  </si>
+  <si>
+    <t>Ce questionnaire vous aide à identifier un programme d’exercices adapté à votre condition physique.</t>
+  </si>
+  <si>
+    <t>Questionnaire d’orientation Move50+ vers un programme d’exercices, utilisable comme support d’échange sans décision automatique.</t>
+  </si>
+  <si>
+    <t>Exemple d’outil d’orientation patient vers un programme d’activité physique.</t>
+  </si>
+  <si>
+    <t>move50plus|questionnaire|orientation|programme|personne_agee|securite|progressivite</t>
+  </si>
+  <si>
+    <t>move50plus-bougez-catalogue-001</t>
+  </si>
+  <si>
+    <t>Move50+ - catalogue Bougez</t>
+  </si>
+  <si>
+    <t>Move50+ - Bougez</t>
+  </si>
+  <si>
+    <t>Page Move50+ regroupant les programmes d’entraînement, séances vidéo et ressources imprimables.</t>
+  </si>
+  <si>
+    <t>patient_library|clinician_library|training_interface|reference_use</t>
+  </si>
+  <si>
+    <t>endurance|renforcement|souplesse|equilibre|motivation</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/bougez/</t>
+  </si>
+  <si>
+    <t>Cette page regroupe les programmes et séances Move50+.</t>
+  </si>
+  <si>
+    <t>Catalogue Move50+ des programmes et séances, utile pour repérer des ressources adaptées.</t>
+  </si>
+  <si>
+    <t>Bibliothèque d’exemples de programmes et séances Move50+.</t>
+  </si>
+  <si>
+    <t>move50plus|bougez|catalogue|videos|programmes|seniors</t>
+  </si>
+  <si>
+    <t>move50plus-programmes-imprimables-001</t>
+  </si>
+  <si>
+    <t>Move50+ - programmes imprimables</t>
+  </si>
+  <si>
+    <t>Page Move50+ regroupant les programmes imprimables et les guides de fixation et suivi d’objectifs.</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/programmes-imprimables-bougez/</t>
+  </si>
+  <si>
+    <t>Cette page regroupe les programmes imprimables Move50+ et les guides de fixation et suivi d’objectifs.</t>
+  </si>
+  <si>
+    <t>Page ressource Move50+ centralisant les PDF imprimables et les outils de suivi d’objectifs.</t>
+  </si>
+  <si>
+    <t>Exemple de page structurée pour accéder à des supports imprimables d’activité physique.</t>
+  </si>
+  <si>
+    <t>move50plus|programmes_imprimables|pdf|objectifs|suivi|seniors</t>
+  </si>
+  <si>
+    <t>move50plus-youtube-chaine-001</t>
+  </si>
+  <si>
+    <t>Move50+ - chaîne YouTube</t>
+  </si>
+  <si>
+    <t>Chaîne YouTube Move50+ regroupant des vidéos de programmes et séances d’activité physique.</t>
+  </si>
+  <si>
+    <t>endurance|renforcement|souplesse|equilibre</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@MOVE50PLUS</t>
+  </si>
+  <si>
+    <t>La chaîne YouTube Move50+ propose des séances vidéo d’activité physique.</t>
+  </si>
+  <si>
+    <t>Chaîne vidéo Move50+ utilisable comme ressource externe de séances d’exercices.</t>
+  </si>
+  <si>
+    <t>Exemple de ressource vidéo patient pour illustrer des programmes d’activité physique.</t>
+  </si>
+  <si>
+    <t>move50plus|youtube|videos|seances|seniors|exercices</t>
+  </si>
+  <si>
+    <t>move50plus-objectifs-fixation-pdf-001</t>
+  </si>
+  <si>
+    <t>Move50+ - guide de fixation d’objectifs</t>
+  </si>
+  <si>
+    <t>Move50+ - fixation d’objectifs</t>
+  </si>
+  <si>
+    <t>PDF Move50+ d’aide à la fixation d’objectifs pour la pratique d’activité physique.</t>
+  </si>
+  <si>
+    <t>motivation|progressivite</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/wp-content/uploads/2019/12/1-guide-fixation-LR.pdf</t>
+  </si>
+  <si>
+    <t>Ce guide imprimable vous aide à formuler un objectif concret d’activité physique.</t>
+  </si>
+  <si>
+    <t>Support patient Move50+ pour aider à structurer un objectif d’activité physique.</t>
+  </si>
+  <si>
+    <t>Exemple d’outil motivationnel de fixation d’objectifs en activité physique.</t>
+  </si>
+  <si>
+    <t>move50plus|objectifs|motivation|pdf|activite_physique|suivi</t>
+  </si>
+  <si>
+    <t>move50plus-objectifs-suivi-pdf-001</t>
+  </si>
+  <si>
+    <t>Move50+ - guide de suivi d’objectif</t>
+  </si>
+  <si>
+    <t>Move50+ - suivi d’objectif</t>
+  </si>
+  <si>
+    <t>PDF Move50+ de suivi de l’atteinte d’un objectif d’activité physique.</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/wp-content/uploads/2019/12/2-guide-suivi-LR.pdf</t>
+  </si>
+  <si>
+    <t>Ce guide imprimable vous aide à faire le point sur l’atteinte de votre objectif d’activité physique.</t>
+  </si>
+  <si>
+    <t>Support patient Move50+ pour accompagner le suivi d’un objectif d’activité physique.</t>
+  </si>
+  <si>
+    <t>Exemple d’outil motivationnel de suivi des objectifs en activité physique.</t>
+  </si>
+  <si>
+    <t>move50plus|suivi|objectifs|motivation|pdf|activite_physique</t>
+  </si>
+  <si>
+    <t>move50plus-sans-limite-programme-001</t>
+  </si>
+  <si>
+    <t>Move50+ - programme Sans limite</t>
+  </si>
+  <si>
+    <t>Move50+ - Sans limite</t>
+  </si>
+  <si>
+    <t>Programme Move50+ visant les personnes très actives, avec séances dynamiques et exercices de type cardio-renforcement.</t>
+  </si>
+  <si>
+    <t>endurance|renforcement|progressivite</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/cours-sans-limite/</t>
+  </si>
+  <si>
+    <t>Programme Move50+ dynamique pour personnes déjà très actives.</t>
+  </si>
+  <si>
+    <t>Programme Move50+ Sans limite : support externe pour patients déjà très actifs.</t>
+  </si>
+  <si>
+    <t>Exemple de programme Move50+ de niveau soutenu.</t>
+  </si>
+  <si>
+    <t>move50plus|sans_limite|cardio|renforcement|endurance|programme</t>
+  </si>
+  <si>
+    <t>move50plus-sans-limite-pdf-001</t>
+  </si>
+  <si>
+    <t>Move50+ - Sans limite - PDF imprimable</t>
+  </si>
+  <si>
+    <t>Sans limite - PDF</t>
+  </si>
+  <si>
+    <t>PDF imprimable du programme Move50+ Sans limite.</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/wp-content/uploads/2019/12/1-sans-limite-LR.pdf</t>
+  </si>
+  <si>
+    <t>PDF imprimable du programme Sans limite.</t>
+  </si>
+  <si>
+    <t>Support imprimable Move50+ du programme Sans limite.</t>
+  </si>
+  <si>
+    <t>Exemple de support imprimable de programme d’exercices.</t>
+  </si>
+  <si>
+    <t>move50plus|sans_limite|pdf|programme|cardio|renforcement</t>
+  </si>
+  <si>
+    <t>move50plus-vitalite-programme-001</t>
+  </si>
+  <si>
+    <t>Move50+ - programme Vitalité</t>
+  </si>
+  <si>
+    <t>Move50+ - Vitalité</t>
+  </si>
+  <si>
+    <t>Programme Move50+ combinant période aérobie et exercices de renforcement principalement debout.</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/cours-vitalite/</t>
+  </si>
+  <si>
+    <t>Programme Move50+ Vitalité, combinant endurance et renforcement.</t>
+  </si>
+  <si>
+    <t>Programme Move50+ Vitalité : support externe d’endurance et renforcement.</t>
+  </si>
+  <si>
+    <t>Exemple de programme mixte endurance-renforcement.</t>
+  </si>
+  <si>
+    <t>move50plus|vitalite|cardio|renforcement|endurance|programme</t>
+  </si>
+  <si>
+    <t>move50plus-vitalite-pdf-001</t>
+  </si>
+  <si>
+    <t>Move50+ - Vitalité - PDF imprimable</t>
+  </si>
+  <si>
+    <t>Vitalité - PDF</t>
+  </si>
+  <si>
+    <t>PDF imprimable du programme Move50+ Vitalité.</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/wp-content/uploads/2019/12/2-Vitalite-LR.pdf</t>
+  </si>
+  <si>
+    <t>PDF imprimable du programme Vitalité.</t>
+  </si>
+  <si>
+    <t>Support imprimable Move50+ du programme Vitalité.</t>
+  </si>
+  <si>
+    <t>Exemple de support imprimable de programme mixte endurance-renforcement.</t>
+  </si>
+  <si>
+    <t>move50plus|vitalite|pdf|programme|endurance|renforcement</t>
+  </si>
+  <si>
+    <t>move50plus-en-douceur-programme-001</t>
+  </si>
+  <si>
+    <t>Move50+ - programme En douceur</t>
+  </si>
+  <si>
+    <t>Move50+ - En douceur</t>
+  </si>
+  <si>
+    <t>Programme Move50+ associant mobilité articulaire, souplesse, force et endurance musculaire avec exercices assis et debout.</t>
+  </si>
+  <si>
+    <t>souplesse|renforcement|progressivite</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/cours-en-douceur/</t>
+  </si>
+  <si>
+    <t>Programme Move50+ En douceur, avec exercices fluides et accessibles.</t>
+  </si>
+  <si>
+    <t>Programme Move50+ En douceur : support externe pour mobilité, souplesse et renforcement léger.</t>
+  </si>
+  <si>
+    <t>Exemple de programme doux favorisant mobilité et souplesse.</t>
+  </si>
+  <si>
+    <t>move50plus|en_douceur|souplesse|mobilite|renforcement|programme</t>
+  </si>
+  <si>
+    <t>move50plus-en-douceur-pdf-001</t>
+  </si>
+  <si>
+    <t>Move50+ - En douceur - PDF imprimable</t>
+  </si>
+  <si>
+    <t>En douceur - PDF</t>
+  </si>
+  <si>
+    <t>PDF imprimable du programme Move50+ En douceur.</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/wp-content/uploads/2019/12/4-en-douceur-LR.pdf</t>
+  </si>
+  <si>
+    <t>PDF imprimable du programme En douceur.</t>
+  </si>
+  <si>
+    <t>Support imprimable Move50+ du programme En douceur.</t>
+  </si>
+  <si>
+    <t>Exemple de support imprimable de programme doux.</t>
+  </si>
+  <si>
+    <t>move50plus|en_douceur|pdf|programme|souplesse|mobilite</t>
+  </si>
+  <si>
+    <t>move50plus-posture-stabilite-programme-001</t>
+  </si>
+  <si>
+    <t>Move50+ - programme Posture et stabilité</t>
+  </si>
+  <si>
+    <t>Move50+ - Posture et stabilité</t>
+  </si>
+  <si>
+    <t>Programme Move50+ ciblant stabilité, équilibre, posture et tonus postural.</t>
+  </si>
+  <si>
+    <t>equilibre|renforcement|souplesse|securite|progressivite</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/cours-posture-et-stabilite/</t>
+  </si>
+  <si>
+    <t>Programme Move50+ Posture et stabilité, centré sur l’équilibre et la stabilité.</t>
+  </si>
+  <si>
+    <t>Programme Move50+ Posture et stabilité : support externe pour équilibre et prévention des chutes.</t>
+  </si>
+  <si>
+    <t>Exemple de programme d’équilibre et stabilité.</t>
+  </si>
+  <si>
+    <t>move50plus|posture|stabilite|equilibre|chute|programme</t>
+  </si>
+  <si>
+    <t>move50plus-posture-stabilite-pdf-001</t>
+  </si>
+  <si>
+    <t>Move50+ - Posture et stabilité - PDF imprimable</t>
+  </si>
+  <si>
+    <t>Posture et stabilité - PDF</t>
+  </si>
+  <si>
+    <t>PDF imprimable du programme Move50+ Posture et stabilité.</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/wp-content/uploads/2019/12/3-posture-stabilite-LR.pdf</t>
+  </si>
+  <si>
+    <t>PDF imprimable du programme Posture et stabilité.</t>
+  </si>
+  <si>
+    <t>Support imprimable Move50+ du programme Posture et stabilité.</t>
+  </si>
+  <si>
+    <t>Exemple de support imprimable de programme équilibre-stabilité.</t>
+  </si>
+  <si>
+    <t>move50plus|posture|stabilite|pdf|equilibre|chute</t>
+  </si>
+  <si>
+    <t>move50plus-sur-chaise-programme-001</t>
+  </si>
+  <si>
+    <t>Move50+ - programme Sur chaise</t>
+  </si>
+  <si>
+    <t>Move50+ - Sur chaise</t>
+  </si>
+  <si>
+    <t>Programme Move50+ d’exercices sur chaise intégrant une période aérobie modérée et des exercices de musculation adaptés.</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/cours-sur-chaise/</t>
+  </si>
+  <si>
+    <t>Programme Move50+ Sur chaise, avec exercices réalisables en position assise.</t>
+  </si>
+  <si>
+    <t>Programme Move50+ Sur chaise : support externe pour exercices adaptés sur chaise.</t>
+  </si>
+  <si>
+    <t>Exemple de programme d’exercices sur chaise.</t>
+  </si>
+  <si>
+    <t>move50plus|sur_chaise|chaise|renforcement|endurance|programme</t>
+  </si>
+  <si>
+    <t>move50plus-sur-chaise-pdf-001</t>
+  </si>
+  <si>
+    <t>Move50+ - Sur chaise - PDF imprimable</t>
+  </si>
+  <si>
+    <t>Sur chaise - PDF</t>
+  </si>
+  <si>
+    <t>PDF imprimable du programme Move50+ Sur chaise.</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/wp-content/uploads/2019/12/5-sur-chaise-LR.pdf</t>
+  </si>
+  <si>
+    <t>PDF imprimable du programme Sur chaise.</t>
+  </si>
+  <si>
+    <t>Support imprimable Move50+ du programme Sur chaise.</t>
+  </si>
+  <si>
+    <t>Exemple de support imprimable de programme sur chaise.</t>
+  </si>
+  <si>
+    <t>move50plus|sur_chaise|pdf|programme|chaise|renforcement</t>
+  </si>
+  <si>
+    <t>move50plus-move-equilibre-programme-001</t>
+  </si>
+  <si>
+    <t>Move50+ - Move en Équilibre</t>
+  </si>
+  <si>
+    <t>Programme Move50+ orienté équilibre, prévention des chutes, flexibilité et renforcement musculaire, structuré en niveaux.</t>
+  </si>
+  <si>
+    <t>https://move50plus.ca/move-en-equilibre/</t>
+  </si>
+  <si>
+    <t>Move en Équilibre propose des séances centrées sur l’équilibre et la prévention des chutes.</t>
+  </si>
+  <si>
+    <t>Programme Move50+ Move en Équilibre : support externe pour équilibre, renforcement et prévention des chutes.</t>
+  </si>
+  <si>
+    <t>Exemple de programme structuré autour de l’équilibre et de la prévention des chutes.</t>
+  </si>
+  <si>
+    <t>move50plus|move_en_equilibre|equilibre|chute|renforcement|seniors</t>
+  </si>
+  <si>
     <t>pathology_id</t>
   </si>
   <si>
@@ -2506,9 +3037,6 @@
     <t>consultation_context</t>
   </si>
   <si>
-    <t>practical_guide</t>
-  </si>
-  <si>
     <t>html</t>
   </si>
   <si>
@@ -2536,9 +3064,6 @@
     <t>additional_reading</t>
   </si>
   <si>
-    <t>self_assessment</t>
-  </si>
-  <si>
     <t>apa_professional</t>
   </si>
   <si>
@@ -2605,536 +3130,128 @@
     <t>reference_use</t>
   </si>
   <si>
-    <t>move50plus-site-principal-001</t>
-  </si>
-  <si>
-    <t>Move50+ - site principal</t>
-  </si>
-  <si>
-    <t>Site Move50+ proposant des programmes d’exercices, un outil d’orientation et des ressources pour rester actif après 50 ans.</t>
-  </si>
-  <si>
-    <t>Move50+ / Sercovie</t>
-  </si>
-  <si>
-    <t>patient|clinician|learner|apa_professional</t>
-  </si>
-  <si>
-    <t>consultation_context|patient_library|clinician_library|training_interface|reference_use</t>
-  </si>
-  <si>
-    <t>endurance|renforcement|souplesse|equilibre|motivation|securite|progressivite</t>
-  </si>
-  <si>
-    <t>geriatrie|medecine_generale|medecine_sport|apa</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/</t>
-  </si>
-  <si>
-    <t>Move50+ propose des programmes d’exercices et des ressources pratiques pour bouger plus, notamment après 50 ans.</t>
-  </si>
-  <si>
-    <t>Site ressource Move50+ utilisable comme bibliothèque de programmes et supports patients.</t>
-  </si>
-  <si>
-    <t>Exemple de plateforme externe de programmes d’activité physique pour patients de plus de 50 ans.</t>
-  </si>
-  <si>
-    <t>Site consulté en juin 2026</t>
-  </si>
-  <si>
-    <t>personne_agee|motivation|reference</t>
-  </si>
-  <si>
-    <t>patient_material_example|reference|additional_reading</t>
-  </si>
-  <si>
-    <t>move50plus|seniors|personne_agee|programme|activite_physique|exercise</t>
-  </si>
-  <si>
-    <t>Ressource externe Move50+ identifiée depuis la fiche patient PAP et les pages Move50+ le 29/06/2026. Ressource non hébergée dans le dépôt PAP.</t>
-  </si>
-  <si>
-    <t>move50plus-questionnaire-orientation-001</t>
-  </si>
-  <si>
-    <t>Move50+ - questionnaire d’orientation vers un programme</t>
-  </si>
-  <si>
-    <t>Move50+ - questionnaire</t>
-  </si>
-  <si>
-    <t>Questionnaire Move50+ guidant le choix d’un programme d’exercices selon la condition physique.</t>
-  </si>
-  <si>
-    <t>motivation|securite|progressivite</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/questionnaire/</t>
-  </si>
-  <si>
-    <t>Ce questionnaire vous aide à identifier un programme d’exercices adapté à votre condition physique.</t>
-  </si>
-  <si>
-    <t>Questionnaire d’orientation Move50+ vers un programme d’exercices, utilisable comme support d’échange sans décision automatique.</t>
-  </si>
-  <si>
-    <t>Exemple d’outil d’orientation patient vers un programme d’activité physique.</t>
-  </si>
-  <si>
-    <t>move50plus|questionnaire|orientation|programme|personne_agee|securite|progressivite</t>
-  </si>
-  <si>
-    <t>move50plus-bougez-catalogue-001</t>
-  </si>
-  <si>
-    <t>Move50+ - catalogue Bougez</t>
-  </si>
-  <si>
-    <t>Move50+ - Bougez</t>
-  </si>
-  <si>
-    <t>Page Move50+ regroupant les programmes d’entraînement, séances vidéo et ressources imprimables.</t>
-  </si>
-  <si>
-    <t>patient_library|clinician_library|training_interface|reference_use</t>
-  </si>
-  <si>
-    <t>endurance|renforcement|souplesse|equilibre|motivation</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/bougez/</t>
-  </si>
-  <si>
-    <t>Cette page regroupe les programmes et séances Move50+.</t>
-  </si>
-  <si>
-    <t>Catalogue Move50+ des programmes et séances, utile pour repérer des ressources adaptées.</t>
-  </si>
-  <si>
-    <t>Bibliothèque d’exemples de programmes et séances Move50+.</t>
-  </si>
-  <si>
-    <t>move50plus|bougez|catalogue|videos|programmes|seniors</t>
-  </si>
-  <si>
-    <t>move50plus-programmes-imprimables-001</t>
-  </si>
-  <si>
-    <t>Move50+ - programmes imprimables</t>
-  </si>
-  <si>
-    <t>Page Move50+ regroupant les programmes imprimables et les guides de fixation et suivi d’objectifs.</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/programmes-imprimables-bougez/</t>
-  </si>
-  <si>
-    <t>Cette page regroupe les programmes imprimables Move50+ et les guides de fixation et suivi d’objectifs.</t>
-  </si>
-  <si>
-    <t>Page ressource Move50+ centralisant les PDF imprimables et les outils de suivi d’objectifs.</t>
-  </si>
-  <si>
-    <t>Exemple de page structurée pour accéder à des supports imprimables d’activité physique.</t>
-  </si>
-  <si>
-    <t>move50plus|programmes_imprimables|pdf|objectifs|suivi|seniors</t>
-  </si>
-  <si>
-    <t>move50plus-youtube-chaine-001</t>
-  </si>
-  <si>
-    <t>Move50+ - chaîne YouTube</t>
-  </si>
-  <si>
-    <t>Chaîne YouTube Move50+ regroupant des vidéos de programmes et séances d’activité physique.</t>
-  </si>
-  <si>
-    <t>endurance|renforcement|souplesse|equilibre</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/@MOVE50PLUS</t>
-  </si>
-  <si>
-    <t>La chaîne YouTube Move50+ propose des séances vidéo d’activité physique.</t>
-  </si>
-  <si>
-    <t>Chaîne vidéo Move50+ utilisable comme ressource externe de séances d’exercices.</t>
-  </si>
-  <si>
-    <t>Exemple de ressource vidéo patient pour illustrer des programmes d’activité physique.</t>
-  </si>
-  <si>
-    <t>move50plus|youtube|videos|seances|seniors|exercices</t>
-  </si>
-  <si>
-    <t>move50plus-objectifs-fixation-pdf-001</t>
-  </si>
-  <si>
-    <t>Move50+ - guide de fixation d’objectifs</t>
-  </si>
-  <si>
-    <t>Move50+ - fixation d’objectifs</t>
-  </si>
-  <si>
-    <t>PDF Move50+ d’aide à la fixation d’objectifs pour la pratique d’activité physique.</t>
-  </si>
-  <si>
-    <t>motivation|progressivite</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/wp-content/uploads/2019/12/1-guide-fixation-LR.pdf</t>
-  </si>
-  <si>
-    <t>Ce guide imprimable vous aide à formuler un objectif concret d’activité physique.</t>
-  </si>
-  <si>
-    <t>Support patient Move50+ pour aider à structurer un objectif d’activité physique.</t>
-  </si>
-  <si>
-    <t>Exemple d’outil motivationnel de fixation d’objectifs en activité physique.</t>
-  </si>
-  <si>
-    <t>move50plus|objectifs|motivation|pdf|activite_physique|suivi</t>
-  </si>
-  <si>
-    <t>move50plus-objectifs-suivi-pdf-001</t>
-  </si>
-  <si>
-    <t>Move50+ - guide de suivi d’objectif</t>
-  </si>
-  <si>
-    <t>Move50+ - suivi d’objectif</t>
-  </si>
-  <si>
-    <t>PDF Move50+ de suivi de l’atteinte d’un objectif d’activité physique.</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/wp-content/uploads/2019/12/2-guide-suivi-LR.pdf</t>
-  </si>
-  <si>
-    <t>Ce guide imprimable vous aide à faire le point sur l’atteinte de votre objectif d’activité physique.</t>
-  </si>
-  <si>
-    <t>Support patient Move50+ pour accompagner le suivi d’un objectif d’activité physique.</t>
-  </si>
-  <si>
-    <t>Exemple d’outil motivationnel de suivi des objectifs en activité physique.</t>
-  </si>
-  <si>
-    <t>move50plus|suivi|objectifs|motivation|pdf|activite_physique</t>
-  </si>
-  <si>
-    <t>move50plus-sans-limite-programme-001</t>
-  </si>
-  <si>
-    <t>Move50+ - programme Sans limite</t>
-  </si>
-  <si>
-    <t>Move50+ - Sans limite</t>
-  </si>
-  <si>
-    <t>Programme Move50+ visant les personnes très actives, avec séances dynamiques et exercices de type cardio-renforcement.</t>
-  </si>
-  <si>
-    <t>endurance|renforcement|progressivite</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/cours-sans-limite/</t>
-  </si>
-  <si>
-    <t>Programme Move50+ dynamique pour personnes déjà très actives.</t>
-  </si>
-  <si>
-    <t>Programme Move50+ Sans limite : support externe pour patients déjà très actifs.</t>
-  </si>
-  <si>
-    <t>Exemple de programme Move50+ de niveau soutenu.</t>
-  </si>
-  <si>
-    <t>move50plus|sans_limite|cardio|renforcement|endurance|programme</t>
-  </si>
-  <si>
-    <t>move50plus-sans-limite-pdf-001</t>
-  </si>
-  <si>
-    <t>Move50+ - Sans limite - PDF imprimable</t>
-  </si>
-  <si>
-    <t>Sans limite - PDF</t>
-  </si>
-  <si>
-    <t>PDF imprimable du programme Move50+ Sans limite.</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/wp-content/uploads/2019/12/1-sans-limite-LR.pdf</t>
-  </si>
-  <si>
-    <t>PDF imprimable du programme Sans limite.</t>
-  </si>
-  <si>
-    <t>Support imprimable Move50+ du programme Sans limite.</t>
-  </si>
-  <si>
-    <t>Exemple de support imprimable de programme d’exercices.</t>
-  </si>
-  <si>
-    <t>move50plus|sans_limite|pdf|programme|cardio|renforcement</t>
-  </si>
-  <si>
-    <t>move50plus-vitalite-programme-001</t>
-  </si>
-  <si>
-    <t>Move50+ - programme Vitalité</t>
-  </si>
-  <si>
-    <t>Move50+ - Vitalité</t>
-  </si>
-  <si>
-    <t>Programme Move50+ combinant période aérobie et exercices de renforcement principalement debout.</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/cours-vitalite/</t>
-  </si>
-  <si>
-    <t>Programme Move50+ Vitalité, combinant endurance et renforcement.</t>
-  </si>
-  <si>
-    <t>Programme Move50+ Vitalité : support externe d’endurance et renforcement.</t>
-  </si>
-  <si>
-    <t>Exemple de programme mixte endurance-renforcement.</t>
-  </si>
-  <si>
-    <t>move50plus|vitalite|cardio|renforcement|endurance|programme</t>
-  </si>
-  <si>
-    <t>move50plus-vitalite-pdf-001</t>
-  </si>
-  <si>
-    <t>Move50+ - Vitalité - PDF imprimable</t>
-  </si>
-  <si>
-    <t>Vitalité - PDF</t>
-  </si>
-  <si>
-    <t>PDF imprimable du programme Move50+ Vitalité.</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/wp-content/uploads/2019/12/2-Vitalite-LR.pdf</t>
-  </si>
-  <si>
-    <t>PDF imprimable du programme Vitalité.</t>
-  </si>
-  <si>
-    <t>Support imprimable Move50+ du programme Vitalité.</t>
-  </si>
-  <si>
-    <t>Exemple de support imprimable de programme mixte endurance-renforcement.</t>
-  </si>
-  <si>
-    <t>move50plus|vitalite|pdf|programme|endurance|renforcement</t>
-  </si>
-  <si>
-    <t>move50plus-en-douceur-programme-001</t>
-  </si>
-  <si>
-    <t>Move50+ - programme En douceur</t>
-  </si>
-  <si>
-    <t>Move50+ - En douceur</t>
-  </si>
-  <si>
-    <t>Programme Move50+ associant mobilité articulaire, souplesse, force et endurance musculaire avec exercices assis et debout.</t>
-  </si>
-  <si>
-    <t>souplesse|renforcement|progressivite</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/cours-en-douceur/</t>
-  </si>
-  <si>
-    <t>Programme Move50+ En douceur, avec exercices fluides et accessibles.</t>
-  </si>
-  <si>
-    <t>Programme Move50+ En douceur : support externe pour mobilité, souplesse et renforcement léger.</t>
-  </si>
-  <si>
-    <t>Exemple de programme doux favorisant mobilité et souplesse.</t>
-  </si>
-  <si>
-    <t>move50plus|en_douceur|souplesse|mobilite|renforcement|programme</t>
-  </si>
-  <si>
-    <t>move50plus-en-douceur-pdf-001</t>
-  </si>
-  <si>
-    <t>Move50+ - En douceur - PDF imprimable</t>
-  </si>
-  <si>
-    <t>En douceur - PDF</t>
-  </si>
-  <si>
-    <t>PDF imprimable du programme Move50+ En douceur.</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/wp-content/uploads/2019/12/4-en-douceur-LR.pdf</t>
-  </si>
-  <si>
-    <t>PDF imprimable du programme En douceur.</t>
-  </si>
-  <si>
-    <t>Support imprimable Move50+ du programme En douceur.</t>
-  </si>
-  <si>
-    <t>Exemple de support imprimable de programme doux.</t>
-  </si>
-  <si>
-    <t>move50plus|en_douceur|pdf|programme|souplesse|mobilite</t>
-  </si>
-  <si>
-    <t>move50plus-posture-stabilite-programme-001</t>
-  </si>
-  <si>
-    <t>Move50+ - programme Posture et stabilité</t>
-  </si>
-  <si>
-    <t>Move50+ - Posture et stabilité</t>
-  </si>
-  <si>
-    <t>Programme Move50+ ciblant stabilité, équilibre, posture et tonus postural.</t>
-  </si>
-  <si>
-    <t>equilibre|renforcement|souplesse|securite|progressivite</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/cours-posture-et-stabilite/</t>
-  </si>
-  <si>
-    <t>Programme Move50+ Posture et stabilité, centré sur l’équilibre et la stabilité.</t>
-  </si>
-  <si>
-    <t>Programme Move50+ Posture et stabilité : support externe pour équilibre et prévention des chutes.</t>
-  </si>
-  <si>
-    <t>Exemple de programme d’équilibre et stabilité.</t>
-  </si>
-  <si>
-    <t>move50plus|posture|stabilite|equilibre|chute|programme</t>
-  </si>
-  <si>
-    <t>move50plus-posture-stabilite-pdf-001</t>
-  </si>
-  <si>
-    <t>Move50+ - Posture et stabilité - PDF imprimable</t>
-  </si>
-  <si>
-    <t>Posture et stabilité - PDF</t>
-  </si>
-  <si>
-    <t>PDF imprimable du programme Move50+ Posture et stabilité.</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/wp-content/uploads/2019/12/3-posture-stabilite-LR.pdf</t>
-  </si>
-  <si>
-    <t>PDF imprimable du programme Posture et stabilité.</t>
-  </si>
-  <si>
-    <t>Support imprimable Move50+ du programme Posture et stabilité.</t>
-  </si>
-  <si>
-    <t>Exemple de support imprimable de programme équilibre-stabilité.</t>
-  </si>
-  <si>
-    <t>move50plus|posture|stabilite|pdf|equilibre|chute</t>
-  </si>
-  <si>
-    <t>move50plus-sur-chaise-programme-001</t>
-  </si>
-  <si>
-    <t>Move50+ - programme Sur chaise</t>
-  </si>
-  <si>
-    <t>Move50+ - Sur chaise</t>
-  </si>
-  <si>
-    <t>Programme Move50+ d’exercices sur chaise intégrant une période aérobie modérée et des exercices de musculation adaptés.</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/cours-sur-chaise/</t>
-  </si>
-  <si>
-    <t>Programme Move50+ Sur chaise, avec exercices réalisables en position assise.</t>
-  </si>
-  <si>
-    <t>Programme Move50+ Sur chaise : support externe pour exercices adaptés sur chaise.</t>
-  </si>
-  <si>
-    <t>Exemple de programme d’exercices sur chaise.</t>
-  </si>
-  <si>
-    <t>move50plus|sur_chaise|chaise|renforcement|endurance|programme</t>
-  </si>
-  <si>
-    <t>move50plus-sur-chaise-pdf-001</t>
-  </si>
-  <si>
-    <t>Move50+ - Sur chaise - PDF imprimable</t>
-  </si>
-  <si>
-    <t>Sur chaise - PDF</t>
-  </si>
-  <si>
-    <t>PDF imprimable du programme Move50+ Sur chaise.</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/wp-content/uploads/2019/12/5-sur-chaise-LR.pdf</t>
-  </si>
-  <si>
-    <t>PDF imprimable du programme Sur chaise.</t>
-  </si>
-  <si>
-    <t>Support imprimable Move50+ du programme Sur chaise.</t>
-  </si>
-  <si>
-    <t>Exemple de support imprimable de programme sur chaise.</t>
-  </si>
-  <si>
-    <t>move50plus|sur_chaise|pdf|programme|chaise|renforcement</t>
-  </si>
-  <si>
-    <t>move50plus-move-equilibre-programme-001</t>
-  </si>
-  <si>
-    <t>Move50+ - Move en Équilibre</t>
-  </si>
-  <si>
-    <t>Programme Move50+ orienté équilibre, prévention des chutes, flexibilité et renforcement musculaire, structuré en niveaux.</t>
-  </si>
-  <si>
-    <t>https://move50plus.ca/move-en-equilibre/</t>
-  </si>
-  <si>
-    <t>Move en Équilibre propose des séances centrées sur l’équilibre et la prévention des chutes.</t>
-  </si>
-  <si>
-    <t>Programme Move50+ Move en Équilibre : support externe pour équilibre, renforcement et prévention des chutes.</t>
-  </si>
-  <si>
-    <t>Exemple de programme structuré autour de l’équilibre et de la prévention des chutes.</t>
-  </si>
-  <si>
-    <t>move50plus|move_en_equilibre|equilibre|chute|renforcement|seniors</t>
+    <t>Colonnes panier / sorties ajoutées</t>
+  </si>
+  <si>
+    <t>output_category</t>
+  </si>
+  <si>
+    <t>Catégorie de classement dans les sorties patient</t>
+  </si>
+  <si>
+    <t>Clé interne affichée ensuite en libellé français</t>
+  </si>
+  <si>
+    <t>basket_default_eligible</t>
+  </si>
+  <si>
+    <t>Ressource éligible à l’ajout manuel au panier</t>
+  </si>
+  <si>
+    <t>true/false ; ne signifie jamais ajout automatique</t>
+  </si>
+  <si>
+    <t>patient_output_allowed</t>
+  </si>
+  <si>
+    <t>Ressource autorisée dans une sortie patient</t>
+  </si>
+  <si>
+    <t>Nécessite toujours sélection explicite du médecin</t>
+  </si>
+  <si>
+    <t>clinician_output_allowed</t>
+  </si>
+  <si>
+    <t>Ressource autorisée dans une sortie médecin</t>
+  </si>
+  <si>
+    <t>CRC/suivi/note médecin selon contexte</t>
+  </si>
+  <si>
+    <t>suggestion_mode</t>
+  </si>
+  <si>
+    <t>Mode de remontée dans l’interface</t>
+  </si>
+  <si>
+    <t>none/library_only/contextual_suggestion/manual_only/pack_candidate</t>
+  </si>
+  <si>
+    <t>pack_ids</t>
+  </si>
+  <si>
+    <t>Packs futurs possibles</t>
+  </si>
+  <si>
+    <t>Préparatoire uniquement ; ne déclenche aucune décision automatique</t>
+  </si>
+  <si>
+    <t>pathologie_situation</t>
+  </si>
+  <si>
+    <t>contextual_suggestion</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>objectifs_suivi</t>
+  </si>
+  <si>
+    <t>evaluer_sa_situation</t>
+  </si>
+  <si>
+    <t>manual_only</t>
+  </si>
+  <si>
+    <t>comprendre_sinformer</t>
+  </si>
+  <si>
+    <t>programmes_exercices</t>
+  </si>
+  <si>
+    <t>equilibre_prevention_chutes</t>
+  </si>
+  <si>
+    <t>sur_chaise_faible_impact</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>debuter_domicile</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>library_only</t>
+  </si>
+  <si>
+    <t>senior_fragile</t>
+  </si>
+  <si>
+    <t>commencer_a_bouger</t>
+  </si>
+  <si>
+    <t>equilibre_chute</t>
+  </si>
+  <si>
+    <t>pack_candidate</t>
+  </si>
+  <si>
+    <t>motivation_suivi</t>
+  </si>
+  <si>
+    <t>qr_liens_utiles</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -3177,6 +3294,13 @@
     <font>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F6000"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -3233,7 +3357,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3312,10 +3436,16 @@
         </x:ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3678,69 +3808,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="6" width="20" customWidth="1"/>
+    <col min="1" max="3" width="32" customWidth="1"/>
+    <col min="4" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="15">
-      <c r="A3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="A3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="24"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
     </row>
     <row r="8" spans="1:6" ht="15">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
     </row>
     <row r="9" spans="1:6" ht="28.5">
       <c r="A9" s="3" t="s">
@@ -3766,7 +3895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="28.5">
+    <row r="12" spans="1:6" ht="42.75">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -3791,16 +3920,16 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
     </row>
-    <row r="17" spans="1:6" ht="30">
+    <row r="17" spans="1:6" ht="15">
       <c r="A17" s="4" t="s">
         <v>17</v>
       </c>
@@ -3821,16 +3950,16 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
     </row>
-    <row r="20" spans="1:6" ht="30">
+    <row r="20" spans="1:6" ht="15">
       <c r="A20" s="5" t="s">
         <v>24</v>
       </c>
@@ -3841,7 +3970,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="28.5">
+    <row r="21" spans="1:6" ht="15">
       <c r="A21" s="5" t="s">
         <v>27</v>
       </c>
@@ -3852,7 +3981,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="42.75">
+    <row r="22" spans="1:6" ht="28.5">
       <c r="A22" s="5" t="s">
         <v>30</v>
       </c>
@@ -3874,7 +4003,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="42.75">
+    <row r="24" spans="1:6" ht="28.5">
       <c r="A24" s="5" t="s">
         <v>35</v>
       </c>
@@ -3886,30 +4015,116 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
+      <c r="A28" s="24" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+    </row>
+    <row r="29" spans="1:6" ht="28.5">
+      <c r="A29" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+    </row>
+    <row r="30" spans="1:6" ht="28.5">
+      <c r="A30" s="19" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+    </row>
+    <row r="31" spans="1:6" ht="28.5">
+      <c r="A31" s="19" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+    </row>
+    <row r="32" spans="1:6" ht="28.5">
+      <c r="A32" s="19" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+    </row>
+    <row r="33" spans="1:6" ht="28.5">
+      <c r="A33" s="19" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+    </row>
+    <row r="34" spans="1:6" ht="42.75">
+      <c r="A34" s="19" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3927,7 +4142,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AX84"/>
+  <dimension ref="A1:BD84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3967,9 +4182,12 @@
     <col min="46" max="48" width="16" customWidth="1"/>
     <col min="49" max="49" width="28" customWidth="1"/>
     <col min="50" max="50" width="40" customWidth="1"/>
+    <col min="51" max="51" width="28" customWidth="1"/>
+    <col min="52" max="55" width="22" customWidth="1"/>
+    <col min="56" max="56" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="42" customHeight="1">
+    <row r="1" spans="1:56" ht="42" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>39</v>
       </c>
@@ -4120,8 +4338,26 @@
       <c r="AX1" s="6" t="s">
         <v>88</v>
       </c>
+      <c r="AY1" s="21" t="s">
+        <v>1034</v>
+      </c>
+      <c r="AZ1" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="BA1" s="21" t="s">
+        <v>1040</v>
+      </c>
+      <c r="BB1" s="21" t="s">
+        <v>1043</v>
+      </c>
+      <c r="BC1" s="21" t="s">
+        <v>1046</v>
+      </c>
+      <c r="BD1" s="21" t="s">
+        <v>1049</v>
+      </c>
     </row>
-    <row r="2" spans="1:50" ht="71.25">
+    <row r="2" spans="1:56" ht="71.25">
       <c r="A2" s="1" t="s">
         <v>89</v>
       </c>
@@ -4250,8 +4486,23 @@
       <c r="AX2" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="AY2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ2" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA2" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB2" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="3" spans="1:50" ht="85.5">
+    <row r="3" spans="1:56" ht="85.5">
       <c r="A3" s="1" t="s">
         <v>116</v>
       </c>
@@ -4380,8 +4631,23 @@
       <c r="AX3" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="AY3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ3" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA3" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB3" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="4" spans="1:50" ht="85.5">
+    <row r="4" spans="1:56" ht="85.5">
       <c r="A4" s="2" t="s">
         <v>129</v>
       </c>
@@ -4510,8 +4776,23 @@
       <c r="AX4" s="2" t="s">
         <v>115</v>
       </c>
+      <c r="AY4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ4" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA4" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB4" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="5" spans="1:50" ht="42.75">
+    <row r="5" spans="1:56" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>143</v>
       </c>
@@ -4630,8 +4911,20 @@
       <c r="AX5" s="1" t="s">
         <v>163</v>
       </c>
+      <c r="AZ5" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>1054</v>
+      </c>
     </row>
-    <row r="6" spans="1:50" ht="28.5">
+    <row r="6" spans="1:56" ht="28.5">
       <c r="A6" s="1" t="s">
         <v>164</v>
       </c>
@@ -4746,8 +5039,20 @@
       <c r="AX6" s="1" t="s">
         <v>163</v>
       </c>
+      <c r="AZ6" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>1054</v>
+      </c>
     </row>
-    <row r="7" spans="1:50" ht="72">
+    <row r="7" spans="1:56" ht="72">
       <c r="A7" s="19" t="s">
         <v>179</v>
       </c>
@@ -4876,8 +5181,23 @@
       <c r="AX7" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ7" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA7" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB7" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="8" spans="1:50" ht="86.25">
+    <row r="8" spans="1:56" ht="86.25">
       <c r="A8" s="19" t="s">
         <v>193</v>
       </c>
@@ -5006,8 +5326,23 @@
       <c r="AX8" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY8" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB8" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="9" spans="1:50" ht="72">
+    <row r="9" spans="1:56" ht="72">
       <c r="A9" s="19" t="s">
         <v>206</v>
       </c>
@@ -5136,8 +5471,23 @@
       <c r="AX9" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY9" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ9" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA9" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB9" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="10" spans="1:50" ht="72">
+    <row r="10" spans="1:56" ht="72">
       <c r="A10" s="19" t="s">
         <v>218</v>
       </c>
@@ -5266,8 +5616,23 @@
       <c r="AX10" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY10" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ10" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA10" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB10" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="11" spans="1:50" ht="72">
+    <row r="11" spans="1:56" ht="72">
       <c r="A11" s="19" t="s">
         <v>229</v>
       </c>
@@ -5396,8 +5761,23 @@
       <c r="AX11" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY11" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ11" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA11" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB11" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="12" spans="1:50" ht="72">
+    <row r="12" spans="1:56" ht="72">
       <c r="A12" s="19" t="s">
         <v>241</v>
       </c>
@@ -5526,8 +5906,23 @@
       <c r="AX12" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ12" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA12" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB12" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="13" spans="1:50" ht="72">
+    <row r="13" spans="1:56" ht="72">
       <c r="A13" s="19" t="s">
         <v>254</v>
       </c>
@@ -5656,8 +6051,23 @@
       <c r="AX13" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY13" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ13" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA13" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB13" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="14" spans="1:50" ht="72">
+    <row r="14" spans="1:56" ht="72">
       <c r="A14" s="19" t="s">
         <v>265</v>
       </c>
@@ -5786,8 +6196,23 @@
       <c r="AX14" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY14" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ14" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA14" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB14" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="15" spans="1:50" ht="72">
+    <row r="15" spans="1:56" ht="72">
       <c r="A15" s="19" t="s">
         <v>276</v>
       </c>
@@ -5916,8 +6341,23 @@
       <c r="AX15" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY15" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ15" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA15" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB15" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC15" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="16" spans="1:50" ht="86.25">
+    <row r="16" spans="1:56" ht="86.25">
       <c r="A16" s="19" t="s">
         <v>287</v>
       </c>
@@ -6046,8 +6486,23 @@
       <c r="AX16" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY16" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ16" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA16" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB16" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC16" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="17" spans="1:50" ht="72">
+    <row r="17" spans="1:55" ht="72">
       <c r="A17" s="19" t="s">
         <v>299</v>
       </c>
@@ -6176,8 +6631,23 @@
       <c r="AX17" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY17" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ17" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA17" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB17" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC17" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="18" spans="1:50" ht="86.25">
+    <row r="18" spans="1:55" ht="86.25">
       <c r="A18" s="19" t="s">
         <v>311</v>
       </c>
@@ -6306,8 +6776,23 @@
       <c r="AX18" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY18" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ18" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA18" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB18" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC18" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="19" spans="1:50" ht="72">
+    <row r="19" spans="1:55" ht="72">
       <c r="A19" s="19" t="s">
         <v>322</v>
       </c>
@@ -6436,8 +6921,23 @@
       <c r="AX19" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY19" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ19" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA19" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB19" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="20" spans="1:50" ht="72">
+    <row r="20" spans="1:55" ht="72">
       <c r="A20" s="19" t="s">
         <v>334</v>
       </c>
@@ -6566,8 +7066,23 @@
       <c r="AX20" s="19" t="s">
         <v>192</v>
       </c>
+      <c r="AY20" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ20" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA20" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB20" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC20" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="21" spans="1:50" ht="86.25">
+    <row r="21" spans="1:55" ht="86.25">
       <c r="A21" s="19" t="s">
         <v>345</v>
       </c>
@@ -6696,8 +7211,23 @@
       <c r="AX21" s="19" t="s">
         <v>357</v>
       </c>
+      <c r="AY21" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AZ21" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA21" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB21" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC21" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="22" spans="1:50">
+    <row r="22" spans="1:55">
       <c r="A22" t="s">
         <v>358</v>
       </c>
@@ -6806,8 +7336,20 @@
       <c r="AX22" t="s">
         <v>373</v>
       </c>
+      <c r="AZ22" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA22" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB22" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC22" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="23" spans="1:50">
+    <row r="23" spans="1:55">
       <c r="A23" t="s">
         <v>374</v>
       </c>
@@ -6916,8 +7458,20 @@
       <c r="AX23" t="s">
         <v>373</v>
       </c>
+      <c r="AZ23" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA23" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB23" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC23" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="24" spans="1:50">
+    <row r="24" spans="1:55">
       <c r="A24" t="s">
         <v>382</v>
       </c>
@@ -7026,8 +7580,20 @@
       <c r="AX24" t="s">
         <v>373</v>
       </c>
+      <c r="AZ24" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA24" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB24" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC24" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="25" spans="1:50">
+    <row r="25" spans="1:55">
       <c r="A25" t="s">
         <v>390</v>
       </c>
@@ -7136,8 +7702,20 @@
       <c r="AX25" t="s">
         <v>373</v>
       </c>
+      <c r="AZ25" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA25" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB25" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC25" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="26" spans="1:50">
+    <row r="26" spans="1:55">
       <c r="A26" t="s">
         <v>397</v>
       </c>
@@ -7246,8 +7824,20 @@
       <c r="AX26" t="s">
         <v>373</v>
       </c>
+      <c r="AZ26" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA26" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB26" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC26" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="27" spans="1:50">
+    <row r="27" spans="1:55">
       <c r="A27" t="s">
         <v>406</v>
       </c>
@@ -7356,8 +7946,20 @@
       <c r="AX27" t="s">
         <v>373</v>
       </c>
+      <c r="AZ27" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA27" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB27" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC27" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="28" spans="1:50">
+    <row r="28" spans="1:55">
       <c r="A28" t="s">
         <v>413</v>
       </c>
@@ -7466,8 +8068,20 @@
       <c r="AX28" t="s">
         <v>373</v>
       </c>
+      <c r="AZ28" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA28" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB28" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC28" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="29" spans="1:50">
+    <row r="29" spans="1:55">
       <c r="A29" t="s">
         <v>421</v>
       </c>
@@ -7576,8 +8190,20 @@
       <c r="AX29" t="s">
         <v>373</v>
       </c>
+      <c r="AZ29" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA29" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB29" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC29" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="30" spans="1:50">
+    <row r="30" spans="1:55">
       <c r="A30" t="s">
         <v>428</v>
       </c>
@@ -7686,8 +8312,20 @@
       <c r="AX30" t="s">
         <v>373</v>
       </c>
+      <c r="AZ30" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA30" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB30" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC30" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="31" spans="1:50">
+    <row r="31" spans="1:55">
       <c r="A31" t="s">
         <v>436</v>
       </c>
@@ -7796,8 +8434,20 @@
       <c r="AX31" t="s">
         <v>373</v>
       </c>
+      <c r="AZ31" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA31" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB31" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC31" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="32" spans="1:50">
+    <row r="32" spans="1:55">
       <c r="A32" t="s">
         <v>443</v>
       </c>
@@ -7906,8 +8556,20 @@
       <c r="AX32" t="s">
         <v>373</v>
       </c>
+      <c r="AZ32" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA32" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB32" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC32" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="33" spans="1:50">
+    <row r="33" spans="1:55">
       <c r="A33" t="s">
         <v>451</v>
       </c>
@@ -8016,8 +8678,20 @@
       <c r="AX33" t="s">
         <v>373</v>
       </c>
+      <c r="AZ33" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA33" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB33" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC33" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="34" spans="1:50">
+    <row r="34" spans="1:55">
       <c r="A34" t="s">
         <v>458</v>
       </c>
@@ -8126,8 +8800,20 @@
       <c r="AX34" t="s">
         <v>373</v>
       </c>
+      <c r="AZ34" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA34" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB34" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC34" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="35" spans="1:50">
+    <row r="35" spans="1:55">
       <c r="A35" t="s">
         <v>466</v>
       </c>
@@ -8236,8 +8922,20 @@
       <c r="AX35" t="s">
         <v>373</v>
       </c>
+      <c r="AZ35" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA35" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB35" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC35" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="36" spans="1:50">
+    <row r="36" spans="1:55">
       <c r="A36" t="s">
         <v>473</v>
       </c>
@@ -8346,8 +9044,20 @@
       <c r="AX36" t="s">
         <v>373</v>
       </c>
+      <c r="AZ36" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA36" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB36" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC36" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="37" spans="1:50">
+    <row r="37" spans="1:55">
       <c r="A37" t="s">
         <v>481</v>
       </c>
@@ -8456,8 +9166,20 @@
       <c r="AX37" t="s">
         <v>373</v>
       </c>
+      <c r="AZ37" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA37" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB37" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC37" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="38" spans="1:50">
+    <row r="38" spans="1:55">
       <c r="A38" t="s">
         <v>488</v>
       </c>
@@ -8566,8 +9288,20 @@
       <c r="AX38" t="s">
         <v>373</v>
       </c>
+      <c r="AZ38" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA38" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB38" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC38" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="39" spans="1:50">
+    <row r="39" spans="1:55">
       <c r="A39" t="s">
         <v>496</v>
       </c>
@@ -8676,8 +9410,20 @@
       <c r="AX39" t="s">
         <v>373</v>
       </c>
+      <c r="AZ39" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA39" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB39" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC39" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="40" spans="1:50">
+    <row r="40" spans="1:55">
       <c r="A40" t="s">
         <v>503</v>
       </c>
@@ -8786,8 +9532,20 @@
       <c r="AX40" t="s">
         <v>373</v>
       </c>
+      <c r="AZ40" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA40" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB40" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC40" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="41" spans="1:50">
+    <row r="41" spans="1:55">
       <c r="A41" t="s">
         <v>511</v>
       </c>
@@ -8896,8 +9654,20 @@
       <c r="AX41" t="s">
         <v>373</v>
       </c>
+      <c r="AZ41" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA41" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB41" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC41" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="42" spans="1:50">
+    <row r="42" spans="1:55">
       <c r="A42" t="s">
         <v>518</v>
       </c>
@@ -9006,8 +9776,20 @@
       <c r="AX42" t="s">
         <v>373</v>
       </c>
+      <c r="AZ42" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA42" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB42" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC42" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="43" spans="1:50">
+    <row r="43" spans="1:55">
       <c r="A43" t="s">
         <v>526</v>
       </c>
@@ -9116,8 +9898,20 @@
       <c r="AX43" t="s">
         <v>373</v>
       </c>
+      <c r="AZ43" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA43" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB43" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC43" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="44" spans="1:50">
+    <row r="44" spans="1:55">
       <c r="A44" t="s">
         <v>533</v>
       </c>
@@ -9226,8 +10020,20 @@
       <c r="AX44" t="s">
         <v>373</v>
       </c>
+      <c r="AZ44" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA44" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB44" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC44" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="45" spans="1:50">
+    <row r="45" spans="1:55">
       <c r="A45" t="s">
         <v>543</v>
       </c>
@@ -9336,8 +10142,20 @@
       <c r="AX45" t="s">
         <v>373</v>
       </c>
+      <c r="AZ45" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA45" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB45" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC45" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="46" spans="1:50">
+    <row r="46" spans="1:55">
       <c r="A46" t="s">
         <v>550</v>
       </c>
@@ -9446,8 +10264,20 @@
       <c r="AX46" t="s">
         <v>373</v>
       </c>
+      <c r="AZ46" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA46" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB46" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC46" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="47" spans="1:50">
+    <row r="47" spans="1:55">
       <c r="A47" t="s">
         <v>559</v>
       </c>
@@ -9556,8 +10386,20 @@
       <c r="AX47" t="s">
         <v>373</v>
       </c>
+      <c r="AZ47" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA47" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB47" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC47" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="48" spans="1:50">
+    <row r="48" spans="1:55">
       <c r="A48" t="s">
         <v>566</v>
       </c>
@@ -9666,8 +10508,20 @@
       <c r="AX48" t="s">
         <v>373</v>
       </c>
+      <c r="AZ48" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA48" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB48" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC48" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="49" spans="1:50">
+    <row r="49" spans="1:55">
       <c r="A49" t="s">
         <v>575</v>
       </c>
@@ -9776,8 +10630,20 @@
       <c r="AX49" t="s">
         <v>373</v>
       </c>
+      <c r="AZ49" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA49" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB49" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC49" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="50" spans="1:50">
+    <row r="50" spans="1:55">
       <c r="A50" t="s">
         <v>582</v>
       </c>
@@ -9886,8 +10752,20 @@
       <c r="AX50" t="s">
         <v>373</v>
       </c>
+      <c r="AZ50" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA50" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB50" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC50" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="51" spans="1:50">
+    <row r="51" spans="1:55">
       <c r="A51" t="s">
         <v>590</v>
       </c>
@@ -9996,8 +10874,20 @@
       <c r="AX51" t="s">
         <v>373</v>
       </c>
+      <c r="AZ51" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA51" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB51" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC51" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="52" spans="1:50">
+    <row r="52" spans="1:55">
       <c r="A52" t="s">
         <v>597</v>
       </c>
@@ -10106,8 +10996,20 @@
       <c r="AX52" t="s">
         <v>373</v>
       </c>
+      <c r="AZ52" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA52" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB52" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC52" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="53" spans="1:50">
+    <row r="53" spans="1:55">
       <c r="A53" t="s">
         <v>606</v>
       </c>
@@ -10216,8 +11118,20 @@
       <c r="AX53" t="s">
         <v>373</v>
       </c>
+      <c r="AZ53" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA53" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB53" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC53" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="54" spans="1:50">
+    <row r="54" spans="1:55">
       <c r="A54" t="s">
         <v>613</v>
       </c>
@@ -10326,8 +11240,20 @@
       <c r="AX54" t="s">
         <v>373</v>
       </c>
+      <c r="AZ54" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA54" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB54" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC54" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="55" spans="1:50">
+    <row r="55" spans="1:55">
       <c r="A55" t="s">
         <v>622</v>
       </c>
@@ -10436,8 +11362,20 @@
       <c r="AX55" t="s">
         <v>373</v>
       </c>
+      <c r="AZ55" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA55" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB55" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC55" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="56" spans="1:50">
+    <row r="56" spans="1:55">
       <c r="A56" t="s">
         <v>629</v>
       </c>
@@ -10546,8 +11484,20 @@
       <c r="AX56" t="s">
         <v>373</v>
       </c>
+      <c r="AZ56" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA56" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB56" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC56" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="57" spans="1:50">
+    <row r="57" spans="1:55">
       <c r="A57" t="s">
         <v>638</v>
       </c>
@@ -10656,8 +11606,20 @@
       <c r="AX57" t="s">
         <v>373</v>
       </c>
+      <c r="AZ57" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA57" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB57" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC57" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="58" spans="1:50">
+    <row r="58" spans="1:55">
       <c r="A58" t="s">
         <v>645</v>
       </c>
@@ -10766,8 +11728,20 @@
       <c r="AX58" t="s">
         <v>373</v>
       </c>
+      <c r="AZ58" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA58" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB58" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC58" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="59" spans="1:50">
+    <row r="59" spans="1:55">
       <c r="A59" t="s">
         <v>653</v>
       </c>
@@ -10876,8 +11850,20 @@
       <c r="AX59" t="s">
         <v>373</v>
       </c>
+      <c r="AZ59" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA59" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB59" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC59" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="60" spans="1:50">
+    <row r="60" spans="1:55">
       <c r="A60" t="s">
         <v>660</v>
       </c>
@@ -10986,8 +11972,20 @@
       <c r="AX60" t="s">
         <v>373</v>
       </c>
+      <c r="AZ60" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA60" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB60" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC60" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="61" spans="1:50">
+    <row r="61" spans="1:55">
       <c r="A61" t="s">
         <v>669</v>
       </c>
@@ -11096,8 +12094,20 @@
       <c r="AX61" t="s">
         <v>373</v>
       </c>
+      <c r="AZ61" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA61" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB61" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC61" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="62" spans="1:50">
+    <row r="62" spans="1:55">
       <c r="A62" t="s">
         <v>676</v>
       </c>
@@ -11206,8 +12216,20 @@
       <c r="AX62" t="s">
         <v>373</v>
       </c>
+      <c r="AZ62" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA62" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB62" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC62" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="63" spans="1:50">
+    <row r="63" spans="1:55">
       <c r="A63" t="s">
         <v>684</v>
       </c>
@@ -11316,8 +12338,20 @@
       <c r="AX63" t="s">
         <v>373</v>
       </c>
+      <c r="AZ63" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA63" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB63" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC63" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="64" spans="1:50">
+    <row r="64" spans="1:55">
       <c r="A64" t="s">
         <v>693</v>
       </c>
@@ -11426,8 +12460,20 @@
       <c r="AX64" t="s">
         <v>373</v>
       </c>
+      <c r="AZ64" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA64" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB64" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC64" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="65" spans="1:50">
+    <row r="65" spans="1:55">
       <c r="A65" t="s">
         <v>701</v>
       </c>
@@ -11536,8 +12582,20 @@
       <c r="AX65" t="s">
         <v>373</v>
       </c>
+      <c r="AZ65" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA65" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB65" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC65" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="66" spans="1:50">
+    <row r="66" spans="1:55">
       <c r="A66" t="s">
         <v>711</v>
       </c>
@@ -11646,66 +12704,78 @@
       <c r="AX66" t="s">
         <v>373</v>
       </c>
+      <c r="AZ66" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA66" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB66" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC66" t="s">
+        <v>1053</v>
+      </c>
     </row>
-    <row r="67" spans="1:50" ht="57.75">
+    <row r="67" spans="1:55" ht="57.75">
       <c r="A67" s="19" t="s">
-        <v>858</v>
+        <v>721</v>
       </c>
       <c r="B67" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>859</v>
+        <v>722</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>859</v>
+        <v>722</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>860</v>
+        <v>723</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H67" s="19" t="s">
         <v>363</v>
       </c>
       <c r="I67" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J67" s="19" t="s">
-        <v>863</v>
+        <v>727</v>
       </c>
       <c r="K67" s="19"/>
       <c r="L67" s="19" t="s">
-        <v>864</v>
+        <v>728</v>
       </c>
       <c r="M67" s="19"/>
       <c r="N67" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O67" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P67" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q67" s="19" t="s">
-        <v>866</v>
+        <v>730</v>
       </c>
       <c r="R67" s="19"/>
       <c r="S67" s="19"/>
       <c r="T67" s="19" t="s">
-        <v>867</v>
+        <v>731</v>
       </c>
       <c r="U67" s="19" t="s">
-        <v>868</v>
+        <v>732</v>
       </c>
       <c r="V67" s="19"/>
       <c r="W67" s="19" t="s">
-        <v>869</v>
+        <v>733</v>
       </c>
       <c r="X67" s="20" t="b">
         <v>1</v>
@@ -11720,7 +12790,7 @@
         <v>0</v>
       </c>
       <c r="AB67" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC67" s="19"/>
       <c r="AD67" s="19">
@@ -11740,20 +12810,20 @@
       </c>
       <c r="AI67" s="19"/>
       <c r="AJ67" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK67" s="19"/>
       <c r="AL67" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM67" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN67" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO67" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP67" s="19"/>
       <c r="AQ67" s="19"/>
@@ -11769,71 +12839,86 @@
         <v>700</v>
       </c>
       <c r="AW67" s="19" t="s">
-        <v>873</v>
+        <v>737</v>
       </c>
       <c r="AX67" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY67" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AZ67" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA67" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB67" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC67" t="s">
+        <v>1053</v>
       </c>
     </row>
-    <row r="68" spans="1:50" ht="57.75">
+    <row r="68" spans="1:55" ht="57.75">
       <c r="A68" s="19" t="s">
-        <v>875</v>
+        <v>739</v>
       </c>
       <c r="B68" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>876</v>
+        <v>740</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>877</v>
+        <v>741</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>878</v>
+        <v>742</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>835</v>
+        <v>743</v>
       </c>
       <c r="H68" s="19" t="s">
         <v>363</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J68" s="19" t="s">
-        <v>863</v>
+        <v>727</v>
       </c>
       <c r="K68" s="19"/>
       <c r="L68" s="19" t="s">
-        <v>879</v>
+        <v>744</v>
       </c>
       <c r="M68" s="19"/>
       <c r="N68" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O68" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P68" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q68" s="19" t="s">
-        <v>880</v>
+        <v>745</v>
       </c>
       <c r="R68" s="19"/>
       <c r="S68" s="19"/>
       <c r="T68" s="19" t="s">
-        <v>881</v>
+        <v>746</v>
       </c>
       <c r="U68" s="19" t="s">
-        <v>882</v>
+        <v>747</v>
       </c>
       <c r="V68" s="19"/>
       <c r="W68" s="19" t="s">
-        <v>883</v>
+        <v>748</v>
       </c>
       <c r="X68" s="20" t="b">
         <v>1</v>
@@ -11848,7 +12933,7 @@
         <v>0</v>
       </c>
       <c r="AB68" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC68" s="19"/>
       <c r="AD68" s="19">
@@ -11868,20 +12953,20 @@
       </c>
       <c r="AI68" s="19"/>
       <c r="AJ68" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK68" s="19"/>
       <c r="AL68" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM68" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN68" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO68" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP68" s="19"/>
       <c r="AQ68" s="19"/>
@@ -11897,71 +12982,86 @@
         <v>710</v>
       </c>
       <c r="AW68" s="19" t="s">
-        <v>884</v>
+        <v>749</v>
       </c>
       <c r="AX68" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY68" t="s">
+        <v>1056</v>
+      </c>
+      <c r="AZ68" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA68" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB68" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC68" t="s">
+        <v>1053</v>
       </c>
     </row>
-    <row r="69" spans="1:50" ht="57.75">
+    <row r="69" spans="1:55" ht="57.75">
       <c r="A69" s="19" t="s">
-        <v>885</v>
+        <v>750</v>
       </c>
       <c r="B69" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>886</v>
+        <v>751</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>887</v>
+        <v>752</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>888</v>
+        <v>753</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G69" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H69" s="19" t="s">
         <v>363</v>
       </c>
       <c r="I69" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J69" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K69" s="19"/>
       <c r="L69" s="19" t="s">
-        <v>890</v>
+        <v>755</v>
       </c>
       <c r="M69" s="19"/>
       <c r="N69" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O69" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P69" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q69" s="19" t="s">
-        <v>891</v>
+        <v>756</v>
       </c>
       <c r="R69" s="19"/>
       <c r="S69" s="19"/>
       <c r="T69" s="19" t="s">
-        <v>892</v>
+        <v>757</v>
       </c>
       <c r="U69" s="19" t="s">
-        <v>893</v>
+        <v>758</v>
       </c>
       <c r="V69" s="19"/>
       <c r="W69" s="19" t="s">
-        <v>894</v>
+        <v>759</v>
       </c>
       <c r="X69" s="20" t="b">
         <v>1</v>
@@ -11976,7 +13076,7 @@
         <v>0</v>
       </c>
       <c r="AB69" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC69" s="19"/>
       <c r="AD69" s="19">
@@ -11996,20 +13096,20 @@
       </c>
       <c r="AI69" s="19"/>
       <c r="AJ69" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK69" s="19"/>
       <c r="AL69" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM69" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN69" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO69" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP69" s="19"/>
       <c r="AQ69" s="19"/>
@@ -12025,71 +13125,86 @@
         <v>720</v>
       </c>
       <c r="AW69" s="19" t="s">
-        <v>895</v>
+        <v>760</v>
       </c>
       <c r="AX69" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY69" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AZ69" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA69" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB69" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC69" t="s">
+        <v>1057</v>
       </c>
     </row>
-    <row r="70" spans="1:50" ht="57.75">
+    <row r="70" spans="1:55" ht="57.75">
       <c r="A70" s="19" t="s">
-        <v>896</v>
+        <v>761</v>
       </c>
       <c r="B70" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>897</v>
+        <v>762</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>897</v>
+        <v>762</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>898</v>
+        <v>763</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G70" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H70" s="19" t="s">
         <v>363</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J70" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K70" s="19"/>
       <c r="L70" s="19" t="s">
-        <v>890</v>
+        <v>755</v>
       </c>
       <c r="M70" s="19"/>
       <c r="N70" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O70" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P70" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q70" s="19" t="s">
-        <v>899</v>
+        <v>764</v>
       </c>
       <c r="R70" s="19"/>
       <c r="S70" s="19"/>
       <c r="T70" s="19" t="s">
-        <v>900</v>
+        <v>765</v>
       </c>
       <c r="U70" s="19" t="s">
-        <v>901</v>
+        <v>766</v>
       </c>
       <c r="V70" s="19"/>
       <c r="W70" s="19" t="s">
-        <v>902</v>
+        <v>767</v>
       </c>
       <c r="X70" s="20" t="b">
         <v>1</v>
@@ -12104,7 +13219,7 @@
         <v>0</v>
       </c>
       <c r="AB70" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC70" s="19"/>
       <c r="AD70" s="19">
@@ -12124,20 +13239,20 @@
       </c>
       <c r="AI70" s="19"/>
       <c r="AJ70" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK70" s="19"/>
       <c r="AL70" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM70" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN70" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO70" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP70" s="19"/>
       <c r="AQ70" s="19"/>
@@ -12153,30 +13268,45 @@
         <v>730</v>
       </c>
       <c r="AW70" s="19" t="s">
-        <v>903</v>
+        <v>768</v>
       </c>
       <c r="AX70" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY70" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AZ70" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA70" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB70" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC70" t="s">
+        <v>1057</v>
       </c>
     </row>
-    <row r="71" spans="1:50" ht="57.75">
+    <row r="71" spans="1:55" ht="57.75">
       <c r="A71" s="19" t="s">
-        <v>904</v>
+        <v>769</v>
       </c>
       <c r="B71" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>905</v>
+        <v>770</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>905</v>
+        <v>770</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>906</v>
+        <v>771</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G71" s="19" t="s">
         <v>148</v>
@@ -12185,39 +13315,39 @@
         <v>149</v>
       </c>
       <c r="I71" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J71" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K71" s="19"/>
       <c r="L71" s="19" t="s">
-        <v>907</v>
+        <v>772</v>
       </c>
       <c r="M71" s="19"/>
       <c r="N71" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O71" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P71" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q71" s="19" t="s">
-        <v>908</v>
+        <v>773</v>
       </c>
       <c r="R71" s="19"/>
       <c r="S71" s="19"/>
       <c r="T71" s="19" t="s">
-        <v>909</v>
+        <v>774</v>
       </c>
       <c r="U71" s="19" t="s">
-        <v>910</v>
+        <v>775</v>
       </c>
       <c r="V71" s="19"/>
       <c r="W71" s="19" t="s">
-        <v>911</v>
+        <v>776</v>
       </c>
       <c r="X71" s="20" t="b">
         <v>1</v>
@@ -12232,7 +13362,7 @@
         <v>0</v>
       </c>
       <c r="AB71" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC71" s="19"/>
       <c r="AD71" s="19">
@@ -12252,20 +13382,20 @@
       </c>
       <c r="AI71" s="19"/>
       <c r="AJ71" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK71" s="19"/>
       <c r="AL71" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM71" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN71" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO71" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP71" s="19"/>
       <c r="AQ71" s="19"/>
@@ -12281,71 +13411,86 @@
         <v>740</v>
       </c>
       <c r="AW71" s="19" t="s">
-        <v>912</v>
+        <v>777</v>
       </c>
       <c r="AX71" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY71" t="s">
+        <v>1058</v>
+      </c>
+      <c r="AZ71" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA71" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB71" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC71" t="s">
+        <v>1057</v>
       </c>
     </row>
-    <row r="72" spans="1:50" ht="57.75">
+    <row r="72" spans="1:55" ht="57.75">
       <c r="A72" s="19" t="s">
-        <v>913</v>
+        <v>778</v>
       </c>
       <c r="B72" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>914</v>
+        <v>779</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>915</v>
+        <v>780</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>916</v>
+        <v>781</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G72" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H72" s="19" t="s">
         <v>95</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J72" s="19" t="s">
-        <v>863</v>
+        <v>727</v>
       </c>
       <c r="K72" s="19"/>
       <c r="L72" s="19" t="s">
-        <v>917</v>
+        <v>782</v>
       </c>
       <c r="M72" s="19"/>
       <c r="N72" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O72" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P72" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q72" s="19" t="s">
-        <v>918</v>
+        <v>783</v>
       </c>
       <c r="R72" s="19"/>
       <c r="S72" s="19"/>
       <c r="T72" s="19" t="s">
-        <v>919</v>
+        <v>784</v>
       </c>
       <c r="U72" s="19" t="s">
-        <v>920</v>
+        <v>785</v>
       </c>
       <c r="V72" s="19"/>
       <c r="W72" s="19" t="s">
-        <v>921</v>
+        <v>786</v>
       </c>
       <c r="X72" s="20" t="b">
         <v>1</v>
@@ -12360,7 +13505,7 @@
         <v>0</v>
       </c>
       <c r="AB72" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC72" s="19"/>
       <c r="AD72" s="19">
@@ -12380,20 +13525,20 @@
       </c>
       <c r="AI72" s="19"/>
       <c r="AJ72" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK72" s="19"/>
       <c r="AL72" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM72" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN72" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO72" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP72" s="19"/>
       <c r="AQ72" s="19"/>
@@ -12409,71 +13554,86 @@
         <v>750</v>
       </c>
       <c r="AW72" s="19" t="s">
-        <v>922</v>
+        <v>787</v>
       </c>
       <c r="AX72" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY72" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AZ72" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA72" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB72" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC72" t="s">
+        <v>1053</v>
       </c>
     </row>
-    <row r="73" spans="1:50" ht="57.75">
+    <row r="73" spans="1:55" ht="57.75">
       <c r="A73" s="19" t="s">
-        <v>923</v>
+        <v>788</v>
       </c>
       <c r="B73" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>924</v>
+        <v>789</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>925</v>
+        <v>790</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>926</v>
+        <v>791</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G73" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H73" s="19" t="s">
         <v>95</v>
       </c>
       <c r="I73" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J73" s="19" t="s">
-        <v>863</v>
+        <v>727</v>
       </c>
       <c r="K73" s="19"/>
       <c r="L73" s="19" t="s">
-        <v>917</v>
+        <v>782</v>
       </c>
       <c r="M73" s="19"/>
       <c r="N73" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O73" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P73" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q73" s="19" t="s">
-        <v>927</v>
+        <v>792</v>
       </c>
       <c r="R73" s="19"/>
       <c r="S73" s="19"/>
       <c r="T73" s="19" t="s">
-        <v>928</v>
+        <v>793</v>
       </c>
       <c r="U73" s="19" t="s">
-        <v>929</v>
+        <v>794</v>
       </c>
       <c r="V73" s="19"/>
       <c r="W73" s="19" t="s">
-        <v>930</v>
+        <v>795</v>
       </c>
       <c r="X73" s="20" t="b">
         <v>1</v>
@@ -12488,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AB73" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC73" s="19"/>
       <c r="AD73" s="19">
@@ -12508,20 +13668,20 @@
       </c>
       <c r="AI73" s="19"/>
       <c r="AJ73" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK73" s="19"/>
       <c r="AL73" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM73" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN73" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO73" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP73" s="19"/>
       <c r="AQ73" s="19"/>
@@ -12537,71 +13697,86 @@
         <v>760</v>
       </c>
       <c r="AW73" s="19" t="s">
-        <v>931</v>
+        <v>796</v>
       </c>
       <c r="AX73" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY73" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AZ73" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA73" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB73" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC73" t="s">
+        <v>1053</v>
       </c>
     </row>
-    <row r="74" spans="1:50" ht="57.75">
+    <row r="74" spans="1:55" ht="57.75">
       <c r="A74" s="19" t="s">
-        <v>932</v>
+        <v>797</v>
       </c>
       <c r="B74" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>933</v>
+        <v>798</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>934</v>
+        <v>799</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>935</v>
+        <v>800</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H74" s="19" t="s">
         <v>363</v>
       </c>
       <c r="I74" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J74" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K74" s="19"/>
       <c r="L74" s="19" t="s">
-        <v>936</v>
+        <v>801</v>
       </c>
       <c r="M74" s="19"/>
       <c r="N74" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O74" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P74" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q74" s="19" t="s">
-        <v>937</v>
+        <v>802</v>
       </c>
       <c r="R74" s="19"/>
       <c r="S74" s="19"/>
       <c r="T74" s="19" t="s">
-        <v>938</v>
+        <v>803</v>
       </c>
       <c r="U74" s="19" t="s">
-        <v>939</v>
+        <v>804</v>
       </c>
       <c r="V74" s="19"/>
       <c r="W74" s="19" t="s">
-        <v>940</v>
+        <v>805</v>
       </c>
       <c r="X74" s="20" t="b">
         <v>1</v>
@@ -12616,7 +13791,7 @@
         <v>0</v>
       </c>
       <c r="AB74" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC74" s="19"/>
       <c r="AD74" s="19">
@@ -12636,20 +13811,20 @@
       </c>
       <c r="AI74" s="19"/>
       <c r="AJ74" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK74" s="19"/>
       <c r="AL74" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM74" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN74" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO74" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP74" s="19"/>
       <c r="AQ74" s="19"/>
@@ -12665,71 +13840,86 @@
         <v>770</v>
       </c>
       <c r="AW74" s="19" t="s">
-        <v>941</v>
+        <v>806</v>
       </c>
       <c r="AX74" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY74" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AZ74" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA74" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB74" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC74" t="s">
+        <v>1057</v>
       </c>
     </row>
-    <row r="75" spans="1:50" ht="57.75">
+    <row r="75" spans="1:55" ht="57.75">
       <c r="A75" s="19" t="s">
-        <v>942</v>
+        <v>807</v>
       </c>
       <c r="B75" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>943</v>
+        <v>808</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>944</v>
+        <v>809</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>945</v>
+        <v>810</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G75" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H75" s="19" t="s">
         <v>95</v>
       </c>
       <c r="I75" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J75" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K75" s="19"/>
       <c r="L75" s="19" t="s">
-        <v>936</v>
+        <v>801</v>
       </c>
       <c r="M75" s="19"/>
       <c r="N75" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O75" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P75" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q75" s="19" t="s">
-        <v>946</v>
+        <v>811</v>
       </c>
       <c r="R75" s="19"/>
       <c r="S75" s="19"/>
       <c r="T75" s="19" t="s">
-        <v>947</v>
+        <v>812</v>
       </c>
       <c r="U75" s="19" t="s">
-        <v>948</v>
+        <v>813</v>
       </c>
       <c r="V75" s="19"/>
       <c r="W75" s="19" t="s">
-        <v>949</v>
+        <v>814</v>
       </c>
       <c r="X75" s="20" t="b">
         <v>1</v>
@@ -12744,7 +13934,7 @@
         <v>0</v>
       </c>
       <c r="AB75" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC75" s="19"/>
       <c r="AD75" s="19">
@@ -12764,20 +13954,20 @@
       </c>
       <c r="AI75" s="19"/>
       <c r="AJ75" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK75" s="19"/>
       <c r="AL75" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM75" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN75" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO75" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP75" s="19"/>
       <c r="AQ75" s="19"/>
@@ -12793,71 +13983,86 @@
         <v>780</v>
       </c>
       <c r="AW75" s="19" t="s">
-        <v>950</v>
+        <v>815</v>
       </c>
       <c r="AX75" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY75" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AZ75" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA75" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB75" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC75" t="s">
+        <v>1057</v>
       </c>
     </row>
-    <row r="76" spans="1:50" ht="57.75">
+    <row r="76" spans="1:55" ht="57.75">
       <c r="A76" s="19" t="s">
-        <v>951</v>
+        <v>816</v>
       </c>
       <c r="B76" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>952</v>
+        <v>817</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>953</v>
+        <v>818</v>
       </c>
       <c r="E76" s="19" t="s">
-        <v>954</v>
+        <v>819</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H76" s="19" t="s">
         <v>363</v>
       </c>
       <c r="I76" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J76" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K76" s="19"/>
       <c r="L76" s="19" t="s">
-        <v>936</v>
+        <v>801</v>
       </c>
       <c r="M76" s="19"/>
       <c r="N76" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O76" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P76" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q76" s="19" t="s">
-        <v>955</v>
+        <v>820</v>
       </c>
       <c r="R76" s="19"/>
       <c r="S76" s="19"/>
       <c r="T76" s="19" t="s">
-        <v>956</v>
+        <v>821</v>
       </c>
       <c r="U76" s="19" t="s">
-        <v>957</v>
+        <v>822</v>
       </c>
       <c r="V76" s="19"/>
       <c r="W76" s="19" t="s">
-        <v>958</v>
+        <v>823</v>
       </c>
       <c r="X76" s="20" t="b">
         <v>1</v>
@@ -12872,7 +14077,7 @@
         <v>0</v>
       </c>
       <c r="AB76" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC76" s="19"/>
       <c r="AD76" s="19">
@@ -12892,20 +14097,20 @@
       </c>
       <c r="AI76" s="19"/>
       <c r="AJ76" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK76" s="19"/>
       <c r="AL76" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM76" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN76" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO76" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP76" s="19"/>
       <c r="AQ76" s="19"/>
@@ -12921,71 +14126,86 @@
         <v>790</v>
       </c>
       <c r="AW76" s="19" t="s">
-        <v>959</v>
+        <v>824</v>
       </c>
       <c r="AX76" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY76" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AZ76" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA76" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB76" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC76" t="s">
+        <v>1057</v>
       </c>
     </row>
-    <row r="77" spans="1:50" ht="57.75">
+    <row r="77" spans="1:55" ht="57.75">
       <c r="A77" s="19" t="s">
-        <v>960</v>
+        <v>825</v>
       </c>
       <c r="B77" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>961</v>
+        <v>826</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>962</v>
+        <v>827</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>963</v>
+        <v>828</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G77" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H77" s="19" t="s">
         <v>95</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J77" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K77" s="19"/>
       <c r="L77" s="19" t="s">
-        <v>936</v>
+        <v>801</v>
       </c>
       <c r="M77" s="19"/>
       <c r="N77" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O77" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P77" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q77" s="19" t="s">
-        <v>964</v>
+        <v>829</v>
       </c>
       <c r="R77" s="19"/>
       <c r="S77" s="19"/>
       <c r="T77" s="19" t="s">
-        <v>965</v>
+        <v>830</v>
       </c>
       <c r="U77" s="19" t="s">
-        <v>966</v>
+        <v>831</v>
       </c>
       <c r="V77" s="19"/>
       <c r="W77" s="19" t="s">
-        <v>967</v>
+        <v>832</v>
       </c>
       <c r="X77" s="20" t="b">
         <v>1</v>
@@ -13000,7 +14220,7 @@
         <v>0</v>
       </c>
       <c r="AB77" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC77" s="19"/>
       <c r="AD77" s="19">
@@ -13020,20 +14240,20 @@
       </c>
       <c r="AI77" s="19"/>
       <c r="AJ77" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK77" s="19"/>
       <c r="AL77" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM77" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN77" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO77" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP77" s="19"/>
       <c r="AQ77" s="19"/>
@@ -13049,71 +14269,86 @@
         <v>800</v>
       </c>
       <c r="AW77" s="19" t="s">
-        <v>968</v>
+        <v>833</v>
       </c>
       <c r="AX77" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY77" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AZ77" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA77" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB77" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC77" t="s">
+        <v>1057</v>
       </c>
     </row>
-    <row r="78" spans="1:50" ht="57.75">
+    <row r="78" spans="1:55" ht="57.75">
       <c r="A78" s="19" t="s">
-        <v>969</v>
+        <v>834</v>
       </c>
       <c r="B78" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>970</v>
+        <v>835</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>971</v>
+        <v>836</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>972</v>
+        <v>837</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G78" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H78" s="19" t="s">
         <v>363</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J78" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K78" s="19"/>
       <c r="L78" s="19" t="s">
-        <v>973</v>
+        <v>838</v>
       </c>
       <c r="M78" s="19"/>
       <c r="N78" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O78" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P78" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q78" s="19" t="s">
-        <v>974</v>
+        <v>839</v>
       </c>
       <c r="R78" s="19"/>
       <c r="S78" s="19"/>
       <c r="T78" s="19" t="s">
-        <v>975</v>
+        <v>840</v>
       </c>
       <c r="U78" s="19" t="s">
-        <v>976</v>
+        <v>841</v>
       </c>
       <c r="V78" s="19"/>
       <c r="W78" s="19" t="s">
-        <v>977</v>
+        <v>842</v>
       </c>
       <c r="X78" s="20" t="b">
         <v>1</v>
@@ -13128,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="AB78" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC78" s="19"/>
       <c r="AD78" s="19">
@@ -13148,20 +14383,20 @@
       </c>
       <c r="AI78" s="19"/>
       <c r="AJ78" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK78" s="19"/>
       <c r="AL78" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM78" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN78" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO78" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP78" s="19"/>
       <c r="AQ78" s="19"/>
@@ -13177,71 +14412,86 @@
         <v>810</v>
       </c>
       <c r="AW78" s="19" t="s">
-        <v>978</v>
+        <v>843</v>
       </c>
       <c r="AX78" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY78" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AZ78" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA78" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB78" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC78" t="s">
+        <v>1057</v>
       </c>
     </row>
-    <row r="79" spans="1:50" ht="57.75">
+    <row r="79" spans="1:55" ht="57.75">
       <c r="A79" s="19" t="s">
-        <v>979</v>
+        <v>844</v>
       </c>
       <c r="B79" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>980</v>
+        <v>845</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>981</v>
+        <v>846</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>982</v>
+        <v>847</v>
       </c>
       <c r="F79" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H79" s="19" t="s">
         <v>95</v>
       </c>
       <c r="I79" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J79" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K79" s="19"/>
       <c r="L79" s="19" t="s">
-        <v>973</v>
+        <v>838</v>
       </c>
       <c r="M79" s="19"/>
       <c r="N79" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O79" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P79" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q79" s="19" t="s">
-        <v>983</v>
+        <v>848</v>
       </c>
       <c r="R79" s="19"/>
       <c r="S79" s="19"/>
       <c r="T79" s="19" t="s">
-        <v>984</v>
+        <v>849</v>
       </c>
       <c r="U79" s="19" t="s">
-        <v>985</v>
+        <v>850</v>
       </c>
       <c r="V79" s="19"/>
       <c r="W79" s="19" t="s">
-        <v>986</v>
+        <v>851</v>
       </c>
       <c r="X79" s="20" t="b">
         <v>1</v>
@@ -13256,7 +14506,7 @@
         <v>0</v>
       </c>
       <c r="AB79" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC79" s="19"/>
       <c r="AD79" s="19">
@@ -13276,20 +14526,20 @@
       </c>
       <c r="AI79" s="19"/>
       <c r="AJ79" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK79" s="19"/>
       <c r="AL79" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM79" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN79" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO79" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP79" s="19"/>
       <c r="AQ79" s="19"/>
@@ -13305,71 +14555,86 @@
         <v>820</v>
       </c>
       <c r="AW79" s="19" t="s">
-        <v>987</v>
+        <v>852</v>
       </c>
       <c r="AX79" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY79" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AZ79" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA79" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB79" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC79" t="s">
+        <v>1057</v>
       </c>
     </row>
-    <row r="80" spans="1:50" ht="57.75">
+    <row r="80" spans="1:55" ht="57.75">
       <c r="A80" s="19" t="s">
-        <v>988</v>
+        <v>853</v>
       </c>
       <c r="B80" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>989</v>
+        <v>854</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>990</v>
+        <v>855</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>991</v>
+        <v>856</v>
       </c>
       <c r="F80" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H80" s="19" t="s">
         <v>363</v>
       </c>
       <c r="I80" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J80" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K80" s="19"/>
       <c r="L80" s="19" t="s">
-        <v>992</v>
+        <v>857</v>
       </c>
       <c r="M80" s="19"/>
       <c r="N80" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O80" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P80" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q80" s="19" t="s">
-        <v>993</v>
+        <v>858</v>
       </c>
       <c r="R80" s="19"/>
       <c r="S80" s="19"/>
       <c r="T80" s="19" t="s">
-        <v>994</v>
+        <v>859</v>
       </c>
       <c r="U80" s="19" t="s">
-        <v>995</v>
+        <v>860</v>
       </c>
       <c r="V80" s="19"/>
       <c r="W80" s="19" t="s">
-        <v>996</v>
+        <v>861</v>
       </c>
       <c r="X80" s="20" t="b">
         <v>1</v>
@@ -13384,7 +14649,7 @@
         <v>0</v>
       </c>
       <c r="AB80" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC80" s="19"/>
       <c r="AD80" s="19">
@@ -13404,20 +14669,20 @@
       </c>
       <c r="AI80" s="19"/>
       <c r="AJ80" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK80" s="19"/>
       <c r="AL80" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM80" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN80" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO80" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP80" s="19"/>
       <c r="AQ80" s="19"/>
@@ -13433,71 +14698,86 @@
         <v>830</v>
       </c>
       <c r="AW80" s="19" t="s">
-        <v>997</v>
+        <v>862</v>
       </c>
       <c r="AX80" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY80" t="s">
+        <v>1060</v>
+      </c>
+      <c r="AZ80" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA80" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB80" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC80" t="s">
+        <v>1057</v>
       </c>
     </row>
-    <row r="81" spans="1:50" ht="57.75">
+    <row r="81" spans="1:55" ht="57.75">
       <c r="A81" s="19" t="s">
-        <v>998</v>
+        <v>863</v>
       </c>
       <c r="B81" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>999</v>
+        <v>864</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>1000</v>
+        <v>865</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>1001</v>
+        <v>866</v>
       </c>
       <c r="F81" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G81" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H81" s="19" t="s">
         <v>95</v>
       </c>
       <c r="I81" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J81" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K81" s="19"/>
       <c r="L81" s="19" t="s">
-        <v>992</v>
+        <v>857</v>
       </c>
       <c r="M81" s="19"/>
       <c r="N81" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O81" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P81" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q81" s="19" t="s">
-        <v>1002</v>
+        <v>867</v>
       </c>
       <c r="R81" s="19"/>
       <c r="S81" s="19"/>
       <c r="T81" s="19" t="s">
-        <v>1003</v>
+        <v>868</v>
       </c>
       <c r="U81" s="19" t="s">
-        <v>1004</v>
+        <v>869</v>
       </c>
       <c r="V81" s="19"/>
       <c r="W81" s="19" t="s">
-        <v>1005</v>
+        <v>870</v>
       </c>
       <c r="X81" s="20" t="b">
         <v>1</v>
@@ -13512,7 +14792,7 @@
         <v>0</v>
       </c>
       <c r="AB81" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC81" s="19"/>
       <c r="AD81" s="19">
@@ -13532,20 +14812,20 @@
       </c>
       <c r="AI81" s="19"/>
       <c r="AJ81" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK81" s="19"/>
       <c r="AL81" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM81" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN81" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO81" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP81" s="19"/>
       <c r="AQ81" s="19"/>
@@ -13561,42 +14841,57 @@
         <v>840</v>
       </c>
       <c r="AW81" s="19" t="s">
-        <v>1006</v>
+        <v>871</v>
       </c>
       <c r="AX81" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY81" t="s">
+        <v>1060</v>
+      </c>
+      <c r="AZ81" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA81" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB81" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC81" t="s">
+        <v>1057</v>
       </c>
     </row>
-    <row r="82" spans="1:50" ht="57.75">
+    <row r="82" spans="1:55" ht="57.75">
       <c r="A82" s="19" t="s">
-        <v>1007</v>
+        <v>872</v>
       </c>
       <c r="B82" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>1008</v>
+        <v>873</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>1009</v>
+        <v>874</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>1010</v>
+        <v>875</v>
       </c>
       <c r="F82" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G82" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H82" s="19" t="s">
         <v>363</v>
       </c>
       <c r="I82" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J82" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K82" s="19"/>
       <c r="L82" s="19" t="s">
@@ -13607,25 +14902,25 @@
         <v>349</v>
       </c>
       <c r="O82" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P82" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q82" s="19" t="s">
-        <v>1011</v>
+        <v>876</v>
       </c>
       <c r="R82" s="19"/>
       <c r="S82" s="19"/>
       <c r="T82" s="19" t="s">
-        <v>1012</v>
+        <v>877</v>
       </c>
       <c r="U82" s="19" t="s">
-        <v>1013</v>
+        <v>878</v>
       </c>
       <c r="V82" s="19"/>
       <c r="W82" s="19" t="s">
-        <v>1014</v>
+        <v>879</v>
       </c>
       <c r="X82" s="20" t="b">
         <v>1</v>
@@ -13640,7 +14935,7 @@
         <v>0</v>
       </c>
       <c r="AB82" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC82" s="19"/>
       <c r="AD82" s="19">
@@ -13660,20 +14955,20 @@
       </c>
       <c r="AI82" s="19"/>
       <c r="AJ82" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK82" s="19"/>
       <c r="AL82" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM82" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN82" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO82" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP82" s="19"/>
       <c r="AQ82" s="19"/>
@@ -13689,42 +14984,57 @@
         <v>850</v>
       </c>
       <c r="AW82" s="19" t="s">
-        <v>1015</v>
+        <v>880</v>
       </c>
       <c r="AX82" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY82" t="s">
+        <v>1061</v>
+      </c>
+      <c r="AZ82" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA82" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB82" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC82" t="s">
+        <v>1057</v>
       </c>
     </row>
-    <row r="83" spans="1:50" ht="57.75">
+    <row r="83" spans="1:55" ht="57.75">
       <c r="A83" s="19" t="s">
-        <v>1016</v>
+        <v>881</v>
       </c>
       <c r="B83" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>1017</v>
+        <v>882</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>1018</v>
+        <v>883</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>1019</v>
+        <v>884</v>
       </c>
       <c r="F83" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H83" s="19" t="s">
         <v>95</v>
       </c>
       <c r="I83" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J83" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K83" s="19"/>
       <c r="L83" s="19" t="s">
@@ -13735,25 +15045,25 @@
         <v>349</v>
       </c>
       <c r="O83" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P83" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q83" s="19" t="s">
-        <v>1020</v>
+        <v>885</v>
       </c>
       <c r="R83" s="19"/>
       <c r="S83" s="19"/>
       <c r="T83" s="19" t="s">
-        <v>1021</v>
+        <v>886</v>
       </c>
       <c r="U83" s="19" t="s">
-        <v>1022</v>
+        <v>887</v>
       </c>
       <c r="V83" s="19"/>
       <c r="W83" s="19" t="s">
-        <v>1023</v>
+        <v>888</v>
       </c>
       <c r="X83" s="20" t="b">
         <v>1</v>
@@ -13768,7 +15078,7 @@
         <v>0</v>
       </c>
       <c r="AB83" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC83" s="19"/>
       <c r="AD83" s="19">
@@ -13788,20 +15098,20 @@
       </c>
       <c r="AI83" s="19"/>
       <c r="AJ83" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK83" s="19"/>
       <c r="AL83" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM83" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN83" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO83" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP83" s="19"/>
       <c r="AQ83" s="19"/>
@@ -13817,71 +15127,86 @@
         <v>860</v>
       </c>
       <c r="AW83" s="19" t="s">
-        <v>1024</v>
+        <v>889</v>
       </c>
       <c r="AX83" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY83" t="s">
+        <v>1061</v>
+      </c>
+      <c r="AZ83" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA83" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB83" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC83" t="s">
+        <v>1057</v>
       </c>
     </row>
-    <row r="84" spans="1:50" ht="57.75">
+    <row r="84" spans="1:55" ht="57.75">
       <c r="A84" s="19" t="s">
-        <v>1025</v>
+        <v>890</v>
       </c>
       <c r="B84" s="19" t="s">
         <v>21</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>1026</v>
+        <v>891</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>1026</v>
+        <v>891</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>1027</v>
+        <v>892</v>
       </c>
       <c r="F84" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="H84" s="19" t="s">
         <v>363</v>
       </c>
       <c r="I84" s="19" t="s">
-        <v>862</v>
+        <v>726</v>
       </c>
       <c r="J84" s="19" t="s">
-        <v>889</v>
+        <v>754</v>
       </c>
       <c r="K84" s="19"/>
       <c r="L84" s="19" t="s">
-        <v>992</v>
+        <v>857</v>
       </c>
       <c r="M84" s="19"/>
       <c r="N84" s="19" t="s">
         <v>349</v>
       </c>
       <c r="O84" s="19" t="s">
-        <v>865</v>
+        <v>729</v>
       </c>
       <c r="P84" s="19" t="s">
         <v>101</v>
       </c>
       <c r="Q84" s="19" t="s">
-        <v>1028</v>
+        <v>893</v>
       </c>
       <c r="R84" s="19"/>
       <c r="S84" s="19"/>
       <c r="T84" s="19" t="s">
-        <v>1029</v>
+        <v>894</v>
       </c>
       <c r="U84" s="19" t="s">
-        <v>1030</v>
+        <v>895</v>
       </c>
       <c r="V84" s="19"/>
       <c r="W84" s="19" t="s">
-        <v>1031</v>
+        <v>896</v>
       </c>
       <c r="X84" s="20" t="b">
         <v>1</v>
@@ -13896,7 +15221,7 @@
         <v>0</v>
       </c>
       <c r="AB84" s="19" t="s">
-        <v>870</v>
+        <v>734</v>
       </c>
       <c r="AC84" s="19"/>
       <c r="AD84" s="19">
@@ -13916,20 +15241,20 @@
       </c>
       <c r="AI84" s="19"/>
       <c r="AJ84" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AK84" s="19"/>
       <c r="AL84" s="19" t="s">
-        <v>861</v>
+        <v>724</v>
       </c>
       <c r="AM84" s="20" t="b">
         <v>1</v>
       </c>
       <c r="AN84" s="19" t="s">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="AO84" s="19" t="s">
-        <v>872</v>
+        <v>736</v>
       </c>
       <c r="AP84" s="19"/>
       <c r="AQ84" s="19"/>
@@ -13945,10 +15270,25 @@
         <v>870</v>
       </c>
       <c r="AW84" s="19" t="s">
-        <v>1032</v>
+        <v>897</v>
       </c>
       <c r="AX84" s="19" t="s">
-        <v>874</v>
+        <v>738</v>
+      </c>
+      <c r="AY84" t="s">
+        <v>1060</v>
+      </c>
+      <c r="AZ84" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BA84" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB84" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC84" t="s">
+        <v>1057</v>
       </c>
     </row>
   </sheetData>
@@ -13984,7 +15324,7 @@
       <formula>AG3="broken"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="11">
     <dataValidation type="list" sqref="B2:B502" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"draft,review,active,inactive,obsolete,archived"</formula1>
     </dataValidation>
@@ -13997,7 +15337,7 @@
     <dataValidation type="list" sqref="P2:P502" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"external,internal,hybrid"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="Z2:AA502 AM2:AM502 X2:X502" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" sqref="Z2:AA502 AM2:AM502 X2:X502 AZ2:BC84" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AG2:AG502" xr:uid="{00000000-0002-0000-0100-000005000000}">
@@ -14008,6 +15348,15 @@
     </dataValidation>
     <dataValidation type="list" sqref="AK2:AK502" xr:uid="{00000000-0002-0000-0100-000007000000}">
       <formula1>"true,false,unknown"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="AY2:AY84" xr:uid="{00000000-0002-0000-0100-000008000000}">
+      <formula1>"comprendre_sinformer,evaluer_sa_situation,commencer_a_bouger,programmes_exercices,sur_chaise_faible_impact,equilibre_prevention_chutes,objectifs_suivi,pathologie_situation,qr_liens_utiles"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="BD2:BD84" xr:uid="{00000000-0002-0000-0100-00000A000000}">
+      <formula1>"debuter_domicile,senior_fragile,equilibre_chute,hta,dt2,arthrose,motivation_suivi"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="BC2:BC84" xr:uid="{00000000-0002-0000-0100-00000B000000}">
+      <formula1>"none,library_only,contextual_suggestion,manual_only,pack_candidate"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14032,22 +15381,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15">
       <c r="A1" s="6" t="s">
-        <v>721</v>
+        <v>898</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>722</v>
+        <v>899</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>723</v>
+        <v>900</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>724</v>
+        <v>901</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>725</v>
+        <v>902</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -14055,17 +15404,17 @@
         <v>98</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>726</v>
+        <v>903</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>727</v>
+        <v>904</v>
       </c>
       <c r="D2" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>728</v>
+        <v>905</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -14073,17 +15422,17 @@
         <v>315</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>729</v>
+        <v>906</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>727</v>
+        <v>904</v>
       </c>
       <c r="D3" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>728</v>
+        <v>905</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -14091,17 +15440,17 @@
         <v>269</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>730</v>
+        <v>907</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>727</v>
+        <v>904</v>
       </c>
       <c r="D4" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>728</v>
+        <v>905</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.5">
@@ -14109,17 +15458,17 @@
         <v>197</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>731</v>
+        <v>908</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>727</v>
+        <v>904</v>
       </c>
       <c r="D5" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>728</v>
+        <v>905</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -14127,17 +15476,17 @@
         <v>258</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>732</v>
+        <v>909</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>733</v>
+        <v>910</v>
       </c>
       <c r="D6" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>728</v>
+        <v>905</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.5">
@@ -14145,19 +15494,19 @@
         <v>120</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>734</v>
+        <v>911</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>733</v>
+        <v>910</v>
       </c>
       <c r="D7" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>735</v>
+        <v>912</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>736</v>
+        <v>913</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -14165,17 +15514,17 @@
         <v>303</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>737</v>
+        <v>914</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>733</v>
+        <v>910</v>
       </c>
       <c r="D8" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>728</v>
+        <v>905</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.5">
@@ -14183,17 +15532,17 @@
         <v>133</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>738</v>
+        <v>915</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>739</v>
+        <v>916</v>
       </c>
       <c r="D9" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>740</v>
+        <v>917</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.5">
@@ -14201,17 +15550,17 @@
         <v>222</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>741</v>
+        <v>918</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>742</v>
+        <v>919</v>
       </c>
       <c r="D10" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>740</v>
+        <v>917</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.5">
@@ -14219,19 +15568,19 @@
         <v>183</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>743</v>
+        <v>920</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>744</v>
+        <v>921</v>
       </c>
       <c r="D11" s="20" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>745</v>
+        <v>922</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>746</v>
+        <v>923</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.5">
@@ -14239,17 +15588,17 @@
         <v>210</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>747</v>
+        <v>924</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>742</v>
+        <v>919</v>
       </c>
       <c r="D12" s="20" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="19"/>
       <c r="F12" s="19" t="s">
-        <v>746</v>
+        <v>923</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.5">
@@ -14257,19 +15606,19 @@
         <v>233</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>748</v>
+        <v>925</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>749</v>
+        <v>926</v>
       </c>
       <c r="D13" s="20" t="b">
         <v>1</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>750</v>
+        <v>927</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>746</v>
+        <v>923</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.5">
@@ -14277,17 +15626,17 @@
         <v>245</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>751</v>
+        <v>928</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>752</v>
+        <v>929</v>
       </c>
       <c r="D14" s="20" t="b">
         <v>1</v>
       </c>
       <c r="E14" s="19"/>
       <c r="F14" s="19" t="s">
-        <v>746</v>
+        <v>923</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.5">
@@ -14295,17 +15644,17 @@
         <v>280</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>753</v>
+        <v>930</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>744</v>
+        <v>921</v>
       </c>
       <c r="D15" s="20" t="b">
         <v>1</v>
       </c>
       <c r="E15" s="19"/>
       <c r="F15" s="19" t="s">
-        <v>746</v>
+        <v>923</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.5">
@@ -14313,19 +15662,19 @@
         <v>291</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>754</v>
+        <v>931</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>752</v>
+        <v>929</v>
       </c>
       <c r="D16" s="20" t="b">
         <v>1</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>755</v>
+        <v>932</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>746</v>
+        <v>923</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.5">
@@ -14333,17 +15682,17 @@
         <v>326</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>756</v>
+        <v>933</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>757</v>
+        <v>934</v>
       </c>
       <c r="D17" s="20" t="b">
         <v>1</v>
       </c>
       <c r="E17" s="19"/>
       <c r="F17" s="19" t="s">
-        <v>746</v>
+        <v>923</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="28.5">
@@ -14351,19 +15700,19 @@
         <v>338</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>758</v>
+        <v>935</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>757</v>
+        <v>934</v>
       </c>
       <c r="D18" s="20" t="b">
         <v>1</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>759</v>
+        <v>936</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>746</v>
+        <v>923</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="42.75">
@@ -14371,19 +15720,19 @@
         <v>349</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>760</v>
+        <v>937</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>760</v>
+        <v>937</v>
       </c>
       <c r="D19" s="20" t="b">
         <v>1</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>761</v>
+        <v>938</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>762</v>
+        <v>939</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -14391,19 +15740,19 @@
         <v>537</v>
       </c>
       <c r="B20" t="s">
-        <v>763</v>
+        <v>940</v>
       </c>
       <c r="C20" t="s">
-        <v>739</v>
+        <v>916</v>
       </c>
       <c r="D20" s="18" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>764</v>
+        <v>941</v>
       </c>
       <c r="F20" t="s">
-        <v>765</v>
+        <v>942</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -14411,19 +15760,19 @@
         <v>570</v>
       </c>
       <c r="B21" t="s">
-        <v>766</v>
+        <v>943</v>
       </c>
       <c r="C21" t="s">
-        <v>739</v>
+        <v>916</v>
       </c>
       <c r="D21" s="18" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>767</v>
+        <v>944</v>
       </c>
       <c r="F21" t="s">
-        <v>765</v>
+        <v>942</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -14431,19 +15780,19 @@
         <v>601</v>
       </c>
       <c r="B22" t="s">
-        <v>768</v>
+        <v>945</v>
       </c>
       <c r="C22" t="s">
-        <v>744</v>
+        <v>921</v>
       </c>
       <c r="D22" s="18" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>769</v>
+        <v>946</v>
       </c>
       <c r="F22" t="s">
-        <v>765</v>
+        <v>942</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -14451,19 +15800,19 @@
         <v>617</v>
       </c>
       <c r="B23" t="s">
-        <v>770</v>
+        <v>947</v>
       </c>
       <c r="C23" t="s">
-        <v>739</v>
+        <v>916</v>
       </c>
       <c r="D23" s="18" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>771</v>
+        <v>948</v>
       </c>
       <c r="F23" t="s">
-        <v>765</v>
+        <v>942</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -14471,19 +15820,19 @@
         <v>705</v>
       </c>
       <c r="B24" t="s">
-        <v>772</v>
+        <v>949</v>
       </c>
       <c r="C24" t="s">
-        <v>773</v>
+        <v>950</v>
       </c>
       <c r="D24" s="18" t="b">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>774</v>
+        <v>951</v>
       </c>
       <c r="F24" t="s">
-        <v>775</v>
+        <v>952</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -14491,19 +15840,19 @@
         <v>715</v>
       </c>
       <c r="B25" t="s">
-        <v>776</v>
+        <v>953</v>
       </c>
       <c r="C25" t="s">
-        <v>773</v>
+        <v>950</v>
       </c>
       <c r="D25" s="18" t="b">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>777</v>
+        <v>954</v>
       </c>
       <c r="F25" t="s">
-        <v>775</v>
+        <v>952</v>
       </c>
     </row>
   </sheetData>
@@ -14533,13 +15882,13 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15">
       <c r="A1" s="6" t="s">
-        <v>778</v>
+        <v>955</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>722</v>
+        <v>899</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>723</v>
+        <v>900</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>21</v>
@@ -14550,70 +15899,70 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>779</v>
+        <v>956</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>780</v>
+        <v>957</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>781</v>
+        <v>958</v>
       </c>
       <c r="D2" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>782</v>
+        <v>959</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>783</v>
+        <v>960</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>784</v>
+        <v>961</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>781</v>
+        <v>958</v>
       </c>
       <c r="D3" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>785</v>
+        <v>962</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>786</v>
+        <v>963</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>787</v>
+        <v>964</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>781</v>
+        <v>958</v>
       </c>
       <c r="D4" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>788</v>
+        <v>965</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>789</v>
+        <v>966</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>790</v>
+        <v>967</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>781</v>
+        <v>958</v>
       </c>
       <c r="D5" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>791</v>
+        <v>968</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -14621,118 +15970,118 @@
         <v>152</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>792</v>
+        <v>969</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>793</v>
+        <v>970</v>
       </c>
       <c r="D6" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>794</v>
+        <v>971</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>795</v>
+        <v>972</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>796</v>
+        <v>973</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>793</v>
+        <v>970</v>
       </c>
       <c r="D7" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>797</v>
+        <v>974</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>798</v>
+        <v>975</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>799</v>
+        <v>976</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>800</v>
+        <v>977</v>
       </c>
       <c r="D8" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>801</v>
+        <v>978</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>802</v>
+        <v>979</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>803</v>
+        <v>980</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>804</v>
+        <v>981</v>
       </c>
       <c r="D9" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>805</v>
+        <v>982</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>806</v>
+        <v>983</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>807</v>
+        <v>984</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>808</v>
+        <v>985</v>
       </c>
       <c r="D10" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>809</v>
+        <v>986</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>810</v>
+        <v>987</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>811</v>
+        <v>988</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>808</v>
+        <v>985</v>
       </c>
       <c r="D11" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>812</v>
+        <v>989</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>813</v>
+        <v>990</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>814</v>
+        <v>991</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>815</v>
+        <v>992</v>
       </c>
       <c r="D12" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>816</v>
+        <v>993</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -14740,16 +16089,16 @@
         <v>172</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>817</v>
+        <v>994</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>818</v>
+        <v>995</v>
       </c>
       <c r="D13" s="7" t="b">
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>819</v>
+        <v>996</v>
       </c>
     </row>
   </sheetData>
@@ -14767,25 +16116,26 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="8" width="26" customWidth="1"/>
+    <col min="9" max="14" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18">
-      <c r="A1" s="23" t="s">
-        <v>820</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+    <row r="1" spans="1:14" ht="18">
+      <c r="A1" s="25" t="s">
+        <v>997</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
-    <row r="3" spans="1:8" ht="15">
+    <row r="3" spans="1:14" ht="15">
       <c r="A3" s="4" t="s">
         <v>45</v>
       </c>
@@ -14793,10 +16143,10 @@
         <v>46</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>821</v>
+        <v>998</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>822</v>
+        <v>999</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>40</v>
@@ -14808,10 +16158,28 @@
         <v>72</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>823</v>
+        <v>1000</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>1034</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>1040</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>1043</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>1046</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>1049</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
         <v>94</v>
       </c>
@@ -14822,7 +16190,7 @@
         <v>96</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>824</v>
+        <v>1001</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>17</v>
@@ -14836,19 +16204,37 @@
       <c r="H4" s="1" t="s">
         <v>160</v>
       </c>
+      <c r="I4" s="19" t="s">
+        <v>1058</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>1062</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>1062</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>1062</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>1054</v>
+      </c>
+      <c r="N4" s="19" t="s">
+        <v>1063</v>
+      </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>825</v>
+        <v>725</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>826</v>
+        <v>1002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>827</v>
+        <v>1003</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>828</v>
+        <v>1004</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>18</v>
@@ -14857,13 +16243,31 @@
         <v>154</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>829</v>
+        <v>1005</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>830</v>
+        <v>1006</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>1064</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>1064</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>1064</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N5" s="19" t="s">
+        <v>1066</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
         <v>168</v>
       </c>
@@ -14871,126 +16275,198 @@
         <v>363</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>831</v>
+        <v>1007</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>832</v>
+        <v>1008</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>833</v>
+        <v>1009</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>158</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>834</v>
+        <v>1010</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19" t="s">
+        <v>1053</v>
+      </c>
+      <c r="N6" s="19" t="s">
+        <v>1068</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>835</v>
+        <v>743</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>836</v>
+        <v>1011</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>837</v>
+        <v>1012</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>838</v>
+        <v>1013</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>110</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>839</v>
+        <v>1014</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>1059</v>
+      </c>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19" t="s">
+        <v>1057</v>
+      </c>
+      <c r="N7" s="19" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
         <v>148</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>840</v>
+        <v>1015</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>841</v>
+        <v>1016</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>842</v>
+        <v>1017</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>843</v>
+        <v>1018</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>844</v>
+        <v>1019</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19" t="s">
+        <v>1069</v>
+      </c>
+      <c r="N8" s="19" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:14">
       <c r="A9" s="1" t="s">
-        <v>845</v>
+        <v>1020</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>846</v>
+        <v>1021</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>847</v>
+        <v>1022</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>848</v>
+        <v>1023</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>849</v>
+        <v>1024</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>850</v>
+        <v>1025</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>1060</v>
+      </c>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>851</v>
+        <v>1026</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>169</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>852</v>
+        <v>1027</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>853</v>
+        <v>1028</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>1055</v>
+      </c>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19" t="s">
+        <v>1070</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:14">
       <c r="A11" s="1" t="s">
         <v>362</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>854</v>
+        <v>1029</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>834</v>
-      </c>
+        <v>1010</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>1052</v>
+      </c>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>855</v>
+        <v>1030</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>856</v>
+        <v>1031</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>857</v>
-      </c>
+        <v>1032</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:14">
       <c r="B13" s="1" t="s">
-        <v>853</v>
+        <v>1028</v>
       </c>
     </row>
   </sheetData>

--- a/data/resources/source/PAP_Bibliotheque_Ressources_Tableur_Maitre_v1.xlsx
+++ b/data/resources/source/PAP_Bibliotheque_Ressources_Tableur_Maitre_v1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3002577\Desktop\APPLICATION PM AP in progress\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3002577\Documents\DEV\PAP\PAP-Plateforme-dev\data\resources\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8749042-9201-4684-A288-970F535C66D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1BFB79-2513-422F-A3D0-DC3003E262A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="780" windowWidth="24870" windowHeight="8025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="285" yWindow="195" windowWidth="24870" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2971" uniqueCount="1072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="1072">
   <si>
     <t>Bibliothèque de ressources PAP — Tableur maître</t>
   </si>
@@ -4145,7 +4145,7 @@
   <dimension ref="A1:BD84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="45.875" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
@@ -7113,7 +7113,9 @@
       <c r="J21" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="K21" s="19"/>
+      <c r="K21" s="19" t="s">
+        <v>349</v>
+      </c>
       <c r="L21" s="19" t="s">
         <v>184</v>
       </c>

--- a/data/resources/source/PAP_Bibliotheque_Ressources_Tableur_Maitre_v1.xlsx
+++ b/data/resources/source/PAP_Bibliotheque_Ressources_Tableur_Maitre_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3002577\Documents\DEV\PAP\PAP-Plateforme-dev\data\resources\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1BFB79-2513-422F-A3D0-DC3003E262A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0979D6F-1EA6-4EA9-9850-A8AFEE22ECDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="195" windowWidth="24870" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="330" yWindow="1560" windowWidth="24870" windowHeight="6555" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -4145,7 +4145,7 @@
   <dimension ref="A1:BD84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="45.875" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>

--- a/data/resources/source/PAP_Bibliotheque_Ressources_Tableur_Maitre_v1.xlsx
+++ b/data/resources/source/PAP_Bibliotheque_Ressources_Tableur_Maitre_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3002577\Documents\DEV\PAP\PAP-Plateforme-dev\data\resources\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0979D6F-1EA6-4EA9-9850-A8AFEE22ECDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FD6D92-1691-4421-8DA0-E21879CB35C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="1560" windowWidth="24870" windowHeight="6555" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11505" yWindow="1560" windowWidth="13695" windowHeight="13410" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="1072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="1074">
   <si>
     <t>Bibliothèque de ressources PAP — Tableur maître</t>
   </si>
@@ -3245,6 +3245,12 @@
   </si>
   <si>
     <t>qr_liens_utiles</t>
+  </si>
+  <si>
+    <t>programme_pratique</t>
+  </si>
+  <si>
+    <t>optional_resource</t>
   </si>
 </sst>
 </file>
@@ -12847,10 +12853,10 @@
         <v>738</v>
       </c>
       <c r="AY67" t="s">
-        <v>1055</v>
+        <v>1072</v>
       </c>
       <c r="AZ67" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA67" s="18" t="b">
         <v>1</v>
@@ -12859,7 +12865,7 @@
         <v>1</v>
       </c>
       <c r="BC67" t="s">
-        <v>1053</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="68" spans="1:55" ht="57.75">
@@ -12990,10 +12996,10 @@
         <v>738</v>
       </c>
       <c r="AY68" t="s">
-        <v>1056</v>
+        <v>1072</v>
       </c>
       <c r="AZ68" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA68" s="18" t="b">
         <v>1</v>
@@ -13002,7 +13008,7 @@
         <v>1</v>
       </c>
       <c r="BC68" t="s">
-        <v>1053</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="69" spans="1:55" ht="57.75">
@@ -13133,10 +13139,10 @@
         <v>738</v>
       </c>
       <c r="AY69" t="s">
-        <v>1055</v>
+        <v>1072</v>
       </c>
       <c r="AZ69" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA69" s="18" t="b">
         <v>1</v>
@@ -13145,7 +13151,7 @@
         <v>1</v>
       </c>
       <c r="BC69" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="70" spans="1:55" ht="57.75">
@@ -13276,10 +13282,10 @@
         <v>738</v>
       </c>
       <c r="AY70" t="s">
-        <v>1055</v>
+        <v>1072</v>
       </c>
       <c r="AZ70" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA70" s="18" t="b">
         <v>1</v>
@@ -13288,7 +13294,7 @@
         <v>1</v>
       </c>
       <c r="BC70" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="71" spans="1:55" ht="57.75">
@@ -13419,10 +13425,10 @@
         <v>738</v>
       </c>
       <c r="AY71" t="s">
-        <v>1058</v>
+        <v>1072</v>
       </c>
       <c r="AZ71" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA71" s="18" t="b">
         <v>1</v>
@@ -13431,7 +13437,7 @@
         <v>1</v>
       </c>
       <c r="BC71" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="72" spans="1:55" ht="57.75">
@@ -13562,10 +13568,10 @@
         <v>738</v>
       </c>
       <c r="AY72" t="s">
-        <v>1055</v>
+        <v>1072</v>
       </c>
       <c r="AZ72" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA72" s="18" t="b">
         <v>1</v>
@@ -13574,7 +13580,7 @@
         <v>1</v>
       </c>
       <c r="BC72" t="s">
-        <v>1053</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="73" spans="1:55" ht="57.75">
@@ -13705,10 +13711,10 @@
         <v>738</v>
       </c>
       <c r="AY73" t="s">
-        <v>1055</v>
+        <v>1072</v>
       </c>
       <c r="AZ73" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA73" s="18" t="b">
         <v>1</v>
@@ -13717,7 +13723,7 @@
         <v>1</v>
       </c>
       <c r="BC73" t="s">
-        <v>1053</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="74" spans="1:55" ht="57.75">
@@ -13848,10 +13854,10 @@
         <v>738</v>
       </c>
       <c r="AY74" t="s">
-        <v>1059</v>
+        <v>1072</v>
       </c>
       <c r="AZ74" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA74" s="18" t="b">
         <v>1</v>
@@ -13860,7 +13866,7 @@
         <v>1</v>
       </c>
       <c r="BC74" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="75" spans="1:55" ht="57.75">
@@ -13991,10 +13997,10 @@
         <v>738</v>
       </c>
       <c r="AY75" t="s">
-        <v>1059</v>
+        <v>1072</v>
       </c>
       <c r="AZ75" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA75" s="18" t="b">
         <v>1</v>
@@ -14003,7 +14009,7 @@
         <v>1</v>
       </c>
       <c r="BC75" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="76" spans="1:55" ht="57.75">
@@ -14134,10 +14140,10 @@
         <v>738</v>
       </c>
       <c r="AY76" t="s">
-        <v>1059</v>
+        <v>1072</v>
       </c>
       <c r="AZ76" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA76" s="18" t="b">
         <v>1</v>
@@ -14146,7 +14152,7 @@
         <v>1</v>
       </c>
       <c r="BC76" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="77" spans="1:55" ht="57.75">
@@ -14277,10 +14283,10 @@
         <v>738</v>
       </c>
       <c r="AY77" t="s">
-        <v>1059</v>
+        <v>1072</v>
       </c>
       <c r="AZ77" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA77" s="18" t="b">
         <v>1</v>
@@ -14289,7 +14295,7 @@
         <v>1</v>
       </c>
       <c r="BC77" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="78" spans="1:55" ht="57.75">
@@ -14420,10 +14426,10 @@
         <v>738</v>
       </c>
       <c r="AY78" t="s">
-        <v>1059</v>
+        <v>1072</v>
       </c>
       <c r="AZ78" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA78" s="18" t="b">
         <v>1</v>
@@ -14432,7 +14438,7 @@
         <v>1</v>
       </c>
       <c r="BC78" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="79" spans="1:55" ht="57.75">
@@ -14563,10 +14569,10 @@
         <v>738</v>
       </c>
       <c r="AY79" t="s">
-        <v>1059</v>
+        <v>1072</v>
       </c>
       <c r="AZ79" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA79" s="18" t="b">
         <v>1</v>
@@ -14575,7 +14581,7 @@
         <v>1</v>
       </c>
       <c r="BC79" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="80" spans="1:55" ht="57.75">
@@ -14706,10 +14712,10 @@
         <v>738</v>
       </c>
       <c r="AY80" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="AZ80" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA80" s="18" t="b">
         <v>1</v>
@@ -14718,7 +14724,7 @@
         <v>1</v>
       </c>
       <c r="BC80" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="81" spans="1:55" ht="57.75">
@@ -14849,10 +14855,10 @@
         <v>738</v>
       </c>
       <c r="AY81" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="AZ81" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA81" s="18" t="b">
         <v>1</v>
@@ -14861,7 +14867,7 @@
         <v>1</v>
       </c>
       <c r="BC81" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="82" spans="1:55" ht="57.75">
@@ -14992,10 +14998,10 @@
         <v>738</v>
       </c>
       <c r="AY82" t="s">
-        <v>1061</v>
+        <v>1072</v>
       </c>
       <c r="AZ82" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA82" s="18" t="b">
         <v>1</v>
@@ -15004,7 +15010,7 @@
         <v>1</v>
       </c>
       <c r="BC82" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="83" spans="1:55" ht="57.75">
@@ -15135,10 +15141,10 @@
         <v>738</v>
       </c>
       <c r="AY83" t="s">
-        <v>1061</v>
+        <v>1072</v>
       </c>
       <c r="AZ83" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA83" s="18" t="b">
         <v>1</v>
@@ -15147,7 +15153,7 @@
         <v>1</v>
       </c>
       <c r="BC83" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="84" spans="1:55" ht="57.75">
@@ -15278,10 +15284,10 @@
         <v>738</v>
       </c>
       <c r="AY84" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="AZ84" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA84" s="18" t="b">
         <v>1</v>
@@ -15290,7 +15296,7 @@
         <v>1</v>
       </c>
       <c r="BC84" t="s">
-        <v>1057</v>
+        <v>1073</v>
       </c>
     </row>
   </sheetData>
@@ -15339,7 +15345,7 @@
     <dataValidation type="list" sqref="P2:P502" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"external,internal,hybrid"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="Z2:AA502 AM2:AM502 X2:X502 AZ2:BC84" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" sqref="Z2:AA502 AM2:AM502 X2:X502 AZ2:BB84 BC2:BC66" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AG2:AG502" xr:uid="{00000000-0002-0000-0100-000005000000}">
@@ -15351,13 +15357,13 @@
     <dataValidation type="list" sqref="AK2:AK502" xr:uid="{00000000-0002-0000-0100-000007000000}">
       <formula1>"true,false,unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AY2:AY84" xr:uid="{00000000-0002-0000-0100-000008000000}">
+    <dataValidation type="list" sqref="AY2:AY66" xr:uid="{00000000-0002-0000-0100-000008000000}">
       <formula1>"comprendre_sinformer,evaluer_sa_situation,commencer_a_bouger,programmes_exercices,sur_chaise_faible_impact,equilibre_prevention_chutes,objectifs_suivi,pathologie_situation,qr_liens_utiles"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="BD2:BD84" xr:uid="{00000000-0002-0000-0100-00000A000000}">
       <formula1>"debuter_domicile,senior_fragile,equilibre_chute,hta,dt2,arthrose,motivation_suivi"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="BC2:BC84" xr:uid="{00000000-0002-0000-0100-00000B000000}">
+    <dataValidation type="list" sqref="BC2:BC66" xr:uid="{00000000-0002-0000-0100-00000B000000}">
       <formula1>"none,library_only,contextual_suggestion,manual_only,pack_candidate"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/resources/source/PAP_Bibliotheque_Ressources_Tableur_Maitre_v1.xlsx
+++ b/data/resources/source/PAP_Bibliotheque_Ressources_Tableur_Maitre_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3002577\Documents\DEV\PAP\PAP-Plateforme-dev\data\resources\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FD6D92-1691-4421-8DA0-E21879CB35C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D41540C-B195-491E-A5C8-F94FCC2DD2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11505" yWindow="1560" windowWidth="13695" windowHeight="13410" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="1074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3017" uniqueCount="1076">
   <si>
     <t>Bibliothèque de ressources PAP — Tableur maître</t>
   </si>
@@ -3251,6 +3251,12 @@
   </si>
   <si>
     <t>optional_resource</t>
+  </si>
+  <si>
+    <t>reference_professionnelle</t>
+  </si>
+  <si>
+    <t>clinician_reference</t>
   </si>
 </sst>
 </file>
@@ -7344,6 +7350,9 @@
       <c r="AX22" t="s">
         <v>373</v>
       </c>
+      <c r="AY22" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ22" s="18" t="b">
         <v>0</v>
       </c>
@@ -7354,7 +7363,7 @@
         <v>1</v>
       </c>
       <c r="BC22" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="23" spans="1:55">
@@ -7466,6 +7475,9 @@
       <c r="AX23" t="s">
         <v>373</v>
       </c>
+      <c r="AY23" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ23" s="18" t="b">
         <v>0</v>
       </c>
@@ -7476,7 +7488,7 @@
         <v>1</v>
       </c>
       <c r="BC23" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="24" spans="1:55">
@@ -7588,6 +7600,9 @@
       <c r="AX24" t="s">
         <v>373</v>
       </c>
+      <c r="AY24" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ24" s="18" t="b">
         <v>0</v>
       </c>
@@ -7598,7 +7613,7 @@
         <v>1</v>
       </c>
       <c r="BC24" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="25" spans="1:55">
@@ -7710,6 +7725,9 @@
       <c r="AX25" t="s">
         <v>373</v>
       </c>
+      <c r="AY25" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ25" s="18" t="b">
         <v>0</v>
       </c>
@@ -7720,7 +7738,7 @@
         <v>1</v>
       </c>
       <c r="BC25" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="26" spans="1:55">
@@ -7832,6 +7850,9 @@
       <c r="AX26" t="s">
         <v>373</v>
       </c>
+      <c r="AY26" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ26" s="18" t="b">
         <v>0</v>
       </c>
@@ -7842,7 +7863,7 @@
         <v>1</v>
       </c>
       <c r="BC26" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="27" spans="1:55">
@@ -7954,6 +7975,9 @@
       <c r="AX27" t="s">
         <v>373</v>
       </c>
+      <c r="AY27" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ27" s="18" t="b">
         <v>0</v>
       </c>
@@ -7964,7 +7988,7 @@
         <v>1</v>
       </c>
       <c r="BC27" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="28" spans="1:55">
@@ -8076,6 +8100,9 @@
       <c r="AX28" t="s">
         <v>373</v>
       </c>
+      <c r="AY28" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ28" s="18" t="b">
         <v>0</v>
       </c>
@@ -8086,7 +8113,7 @@
         <v>1</v>
       </c>
       <c r="BC28" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="29" spans="1:55">
@@ -8198,6 +8225,9 @@
       <c r="AX29" t="s">
         <v>373</v>
       </c>
+      <c r="AY29" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ29" s="18" t="b">
         <v>0</v>
       </c>
@@ -8208,7 +8238,7 @@
         <v>1</v>
       </c>
       <c r="BC29" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="30" spans="1:55">
@@ -8320,6 +8350,9 @@
       <c r="AX30" t="s">
         <v>373</v>
       </c>
+      <c r="AY30" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ30" s="18" t="b">
         <v>0</v>
       </c>
@@ -8330,7 +8363,7 @@
         <v>1</v>
       </c>
       <c r="BC30" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="31" spans="1:55">
@@ -8442,6 +8475,9 @@
       <c r="AX31" t="s">
         <v>373</v>
       </c>
+      <c r="AY31" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ31" s="18" t="b">
         <v>0</v>
       </c>
@@ -8452,7 +8488,7 @@
         <v>1</v>
       </c>
       <c r="BC31" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="32" spans="1:55">
@@ -8564,6 +8600,9 @@
       <c r="AX32" t="s">
         <v>373</v>
       </c>
+      <c r="AY32" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ32" s="18" t="b">
         <v>0</v>
       </c>
@@ -8574,7 +8613,7 @@
         <v>1</v>
       </c>
       <c r="BC32" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="33" spans="1:55">
@@ -8686,6 +8725,9 @@
       <c r="AX33" t="s">
         <v>373</v>
       </c>
+      <c r="AY33" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ33" s="18" t="b">
         <v>0</v>
       </c>
@@ -8696,7 +8738,7 @@
         <v>1</v>
       </c>
       <c r="BC33" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="34" spans="1:55">
@@ -8808,6 +8850,9 @@
       <c r="AX34" t="s">
         <v>373</v>
       </c>
+      <c r="AY34" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ34" s="18" t="b">
         <v>0</v>
       </c>
@@ -8818,7 +8863,7 @@
         <v>1</v>
       </c>
       <c r="BC34" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="35" spans="1:55">
@@ -8930,6 +8975,9 @@
       <c r="AX35" t="s">
         <v>373</v>
       </c>
+      <c r="AY35" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ35" s="18" t="b">
         <v>0</v>
       </c>
@@ -8940,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="BC35" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="36" spans="1:55">
@@ -9052,6 +9100,9 @@
       <c r="AX36" t="s">
         <v>373</v>
       </c>
+      <c r="AY36" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ36" s="18" t="b">
         <v>0</v>
       </c>
@@ -9062,7 +9113,7 @@
         <v>1</v>
       </c>
       <c r="BC36" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="37" spans="1:55">
@@ -9174,6 +9225,9 @@
       <c r="AX37" t="s">
         <v>373</v>
       </c>
+      <c r="AY37" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ37" s="18" t="b">
         <v>0</v>
       </c>
@@ -9184,7 +9238,7 @@
         <v>1</v>
       </c>
       <c r="BC37" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="38" spans="1:55">
@@ -9296,6 +9350,9 @@
       <c r="AX38" t="s">
         <v>373</v>
       </c>
+      <c r="AY38" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ38" s="18" t="b">
         <v>0</v>
       </c>
@@ -9306,7 +9363,7 @@
         <v>1</v>
       </c>
       <c r="BC38" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="39" spans="1:55">
@@ -9418,6 +9475,9 @@
       <c r="AX39" t="s">
         <v>373</v>
       </c>
+      <c r="AY39" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ39" s="18" t="b">
         <v>0</v>
       </c>
@@ -9428,7 +9488,7 @@
         <v>1</v>
       </c>
       <c r="BC39" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="40" spans="1:55">
@@ -9540,6 +9600,9 @@
       <c r="AX40" t="s">
         <v>373</v>
       </c>
+      <c r="AY40" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ40" s="18" t="b">
         <v>0</v>
       </c>
@@ -9550,7 +9613,7 @@
         <v>1</v>
       </c>
       <c r="BC40" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="41" spans="1:55">
@@ -9662,6 +9725,9 @@
       <c r="AX41" t="s">
         <v>373</v>
       </c>
+      <c r="AY41" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ41" s="18" t="b">
         <v>0</v>
       </c>
@@ -9672,7 +9738,7 @@
         <v>1</v>
       </c>
       <c r="BC41" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="42" spans="1:55">
@@ -9784,6 +9850,9 @@
       <c r="AX42" t="s">
         <v>373</v>
       </c>
+      <c r="AY42" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ42" s="18" t="b">
         <v>0</v>
       </c>
@@ -9794,7 +9863,7 @@
         <v>1</v>
       </c>
       <c r="BC42" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="43" spans="1:55">
@@ -9906,6 +9975,9 @@
       <c r="AX43" t="s">
         <v>373</v>
       </c>
+      <c r="AY43" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ43" s="18" t="b">
         <v>0</v>
       </c>
@@ -9916,7 +9988,7 @@
         <v>1</v>
       </c>
       <c r="BC43" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="44" spans="1:55">
@@ -10028,6 +10100,9 @@
       <c r="AX44" t="s">
         <v>373</v>
       </c>
+      <c r="AY44" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ44" s="18" t="b">
         <v>0</v>
       </c>
@@ -10038,7 +10113,7 @@
         <v>1</v>
       </c>
       <c r="BC44" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="45" spans="1:55">
@@ -10150,6 +10225,9 @@
       <c r="AX45" t="s">
         <v>373</v>
       </c>
+      <c r="AY45" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ45" s="18" t="b">
         <v>0</v>
       </c>
@@ -10160,7 +10238,7 @@
         <v>1</v>
       </c>
       <c r="BC45" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="46" spans="1:55">
@@ -10272,6 +10350,9 @@
       <c r="AX46" t="s">
         <v>373</v>
       </c>
+      <c r="AY46" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ46" s="18" t="b">
         <v>0</v>
       </c>
@@ -10282,7 +10363,7 @@
         <v>1</v>
       </c>
       <c r="BC46" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="47" spans="1:55">
@@ -10394,6 +10475,9 @@
       <c r="AX47" t="s">
         <v>373</v>
       </c>
+      <c r="AY47" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ47" s="18" t="b">
         <v>0</v>
       </c>
@@ -10404,7 +10488,7 @@
         <v>1</v>
       </c>
       <c r="BC47" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="48" spans="1:55">
@@ -10516,6 +10600,9 @@
       <c r="AX48" t="s">
         <v>373</v>
       </c>
+      <c r="AY48" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ48" s="18" t="b">
         <v>0</v>
       </c>
@@ -10526,7 +10613,7 @@
         <v>1</v>
       </c>
       <c r="BC48" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="49" spans="1:55">
@@ -10638,6 +10725,9 @@
       <c r="AX49" t="s">
         <v>373</v>
       </c>
+      <c r="AY49" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ49" s="18" t="b">
         <v>0</v>
       </c>
@@ -10648,7 +10738,7 @@
         <v>1</v>
       </c>
       <c r="BC49" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="50" spans="1:55">
@@ -10760,6 +10850,9 @@
       <c r="AX50" t="s">
         <v>373</v>
       </c>
+      <c r="AY50" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ50" s="18" t="b">
         <v>0</v>
       </c>
@@ -10770,7 +10863,7 @@
         <v>1</v>
       </c>
       <c r="BC50" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="51" spans="1:55">
@@ -10882,6 +10975,9 @@
       <c r="AX51" t="s">
         <v>373</v>
       </c>
+      <c r="AY51" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ51" s="18" t="b">
         <v>0</v>
       </c>
@@ -10892,7 +10988,7 @@
         <v>1</v>
       </c>
       <c r="BC51" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="52" spans="1:55">
@@ -11004,6 +11100,9 @@
       <c r="AX52" t="s">
         <v>373</v>
       </c>
+      <c r="AY52" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ52" s="18" t="b">
         <v>0</v>
       </c>
@@ -11014,7 +11113,7 @@
         <v>1</v>
       </c>
       <c r="BC52" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="53" spans="1:55">
@@ -11126,6 +11225,9 @@
       <c r="AX53" t="s">
         <v>373</v>
       </c>
+      <c r="AY53" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ53" s="18" t="b">
         <v>0</v>
       </c>
@@ -11136,7 +11238,7 @@
         <v>1</v>
       </c>
       <c r="BC53" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="54" spans="1:55">
@@ -11248,6 +11350,9 @@
       <c r="AX54" t="s">
         <v>373</v>
       </c>
+      <c r="AY54" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ54" s="18" t="b">
         <v>0</v>
       </c>
@@ -11258,7 +11363,7 @@
         <v>1</v>
       </c>
       <c r="BC54" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="55" spans="1:55">
@@ -11370,6 +11475,9 @@
       <c r="AX55" t="s">
         <v>373</v>
       </c>
+      <c r="AY55" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ55" s="18" t="b">
         <v>0</v>
       </c>
@@ -11380,7 +11488,7 @@
         <v>1</v>
       </c>
       <c r="BC55" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="56" spans="1:55">
@@ -11492,6 +11600,9 @@
       <c r="AX56" t="s">
         <v>373</v>
       </c>
+      <c r="AY56" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ56" s="18" t="b">
         <v>0</v>
       </c>
@@ -11502,7 +11613,7 @@
         <v>1</v>
       </c>
       <c r="BC56" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="57" spans="1:55">
@@ -11614,6 +11725,9 @@
       <c r="AX57" t="s">
         <v>373</v>
       </c>
+      <c r="AY57" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ57" s="18" t="b">
         <v>0</v>
       </c>
@@ -11624,7 +11738,7 @@
         <v>1</v>
       </c>
       <c r="BC57" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="58" spans="1:55">
@@ -11736,6 +11850,9 @@
       <c r="AX58" t="s">
         <v>373</v>
       </c>
+      <c r="AY58" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ58" s="18" t="b">
         <v>0</v>
       </c>
@@ -11746,7 +11863,7 @@
         <v>1</v>
       </c>
       <c r="BC58" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="59" spans="1:55">
@@ -11858,6 +11975,9 @@
       <c r="AX59" t="s">
         <v>373</v>
       </c>
+      <c r="AY59" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ59" s="18" t="b">
         <v>0</v>
       </c>
@@ -11868,7 +11988,7 @@
         <v>1</v>
       </c>
       <c r="BC59" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="60" spans="1:55">
@@ -11980,6 +12100,9 @@
       <c r="AX60" t="s">
         <v>373</v>
       </c>
+      <c r="AY60" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ60" s="18" t="b">
         <v>0</v>
       </c>
@@ -11990,7 +12113,7 @@
         <v>1</v>
       </c>
       <c r="BC60" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="61" spans="1:55">
@@ -12102,6 +12225,9 @@
       <c r="AX61" t="s">
         <v>373</v>
       </c>
+      <c r="AY61" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ61" s="18" t="b">
         <v>0</v>
       </c>
@@ -12112,7 +12238,7 @@
         <v>1</v>
       </c>
       <c r="BC61" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="62" spans="1:55">
@@ -12224,6 +12350,9 @@
       <c r="AX62" t="s">
         <v>373</v>
       </c>
+      <c r="AY62" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ62" s="18" t="b">
         <v>0</v>
       </c>
@@ -12234,7 +12363,7 @@
         <v>1</v>
       </c>
       <c r="BC62" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="63" spans="1:55">
@@ -12346,6 +12475,9 @@
       <c r="AX63" t="s">
         <v>373</v>
       </c>
+      <c r="AY63" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ63" s="18" t="b">
         <v>0</v>
       </c>
@@ -12356,7 +12488,7 @@
         <v>1</v>
       </c>
       <c r="BC63" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="64" spans="1:55">
@@ -12468,6 +12600,9 @@
       <c r="AX64" t="s">
         <v>373</v>
       </c>
+      <c r="AY64" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ64" s="18" t="b">
         <v>0</v>
       </c>
@@ -12478,7 +12613,7 @@
         <v>1</v>
       </c>
       <c r="BC64" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="65" spans="1:55">
@@ -12590,6 +12725,9 @@
       <c r="AX65" t="s">
         <v>373</v>
       </c>
+      <c r="AY65" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ65" s="18" t="b">
         <v>0</v>
       </c>
@@ -12600,7 +12738,7 @@
         <v>1</v>
       </c>
       <c r="BC65" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="66" spans="1:55">
@@ -12712,6 +12850,9 @@
       <c r="AX66" t="s">
         <v>373</v>
       </c>
+      <c r="AY66" t="s">
+        <v>1074</v>
+      </c>
       <c r="AZ66" s="18" t="b">
         <v>0</v>
       </c>
@@ -12722,7 +12863,7 @@
         <v>1</v>
       </c>
       <c r="BC66" t="s">
-        <v>1053</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="67" spans="1:55" ht="57.75">
@@ -15345,7 +15486,7 @@
     <dataValidation type="list" sqref="P2:P502" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"external,internal,hybrid"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="Z2:AA502 AM2:AM502 X2:X502 AZ2:BB84 BC2:BC66" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" sqref="Z2:AA502 AM2:AM502 X2:X502 AZ2:BB84 BC2:BC21" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>"true,false"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="AG2:AG502" xr:uid="{00000000-0002-0000-0100-000005000000}">
@@ -15357,13 +15498,13 @@
     <dataValidation type="list" sqref="AK2:AK502" xr:uid="{00000000-0002-0000-0100-000007000000}">
       <formula1>"true,false,unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AY2:AY66" xr:uid="{00000000-0002-0000-0100-000008000000}">
+    <dataValidation type="list" sqref="AY2:AY21" xr:uid="{00000000-0002-0000-0100-000008000000}">
       <formula1>"comprendre_sinformer,evaluer_sa_situation,commencer_a_bouger,programmes_exercices,sur_chaise_faible_impact,equilibre_prevention_chutes,objectifs_suivi,pathologie_situation,qr_liens_utiles"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="BD2:BD84" xr:uid="{00000000-0002-0000-0100-00000A000000}">
       <formula1>"debuter_domicile,senior_fragile,equilibre_chute,hta,dt2,arthrose,motivation_suivi"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="BC2:BC66" xr:uid="{00000000-0002-0000-0100-00000B000000}">
+    <dataValidation type="list" sqref="BC2:BC21" xr:uid="{00000000-0002-0000-0100-00000B000000}">
       <formula1>"none,library_only,contextual_suggestion,manual_only,pack_candidate"</formula1>
     </dataValidation>
   </dataValidations>
